--- a/public/files/MAP/MAP002.xlsx
+++ b/public/files/MAP/MAP002.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\MAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EB0113-8B91-493E-BFEE-7CAD0F1AF017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29024339-52A9-4892-B016-6184B7687BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="26205" windowHeight="14850" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
+    <workbookView xWindow="1320" yWindow="750" windowWidth="26205" windowHeight="14850" activeTab="5" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
   </bookViews>
   <sheets>
     <sheet name="MAP" sheetId="3" r:id="rId1"/>
-    <sheet name="MAP_ELV" sheetId="6" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId3"/>
-    <sheet name="visual" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId2"/>
+    <sheet name="MAP_ELV" sheetId="6" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId4"/>
+    <sheet name="visual" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="188">
   <si>
     <t>##このページは人間が確認するための疑似ヘクスマップ</t>
     <rPh sb="8" eb="10">
@@ -53,10 +55,6 @@
     <t>59f</t>
   </si>
   <si>
-    <t>59f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>58f</t>
   </si>
   <si>
@@ -1102,6 +1100,103 @@
   </si>
   <si>
     <t>ｲﾛ ｲｯｶｲﾂﾞﾂ　53F</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>街・石・樹・骨・氷・顔・炎・金・異・外・黒・赤・青・黄・緑・紫・白</t>
+  </si>
+  <si>
+    <t>樹</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金</t>
+    <rPh sb="0" eb="1">
+      <t>カネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Face area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CIty area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Boulders area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Treeland area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Skeleton area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Iceland area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fire area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Golden City area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Arien area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Outside area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Black Onix area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fire Crystal area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Abyss Beryl area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Forest Malachite area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eclair Amber area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aqua Quartz area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Moon Stone area</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GCA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスプロセル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロセル</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1109,7 +1204,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1194,6 +1289,11 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1263,7 +1363,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1329,6 +1429,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1662,10 +1765,10 @@
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1674,131 +1777,133 @@
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>81</v>
-      </c>
       <c r="D3" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" s="9"/>
       <c r="H3" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" t="s">
         <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
       </c>
       <c r="F5" s="9"/>
       <c r="H5" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="D6" t="s">
         <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7" s="9"/>
       <c r="H7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" t="s">
         <v>131</v>
-      </c>
-      <c r="I7" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F9" s="9"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>52</v>
+      </c>
       <c r="K9" s="4"/>
     </row>
     <row r="10" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
@@ -1809,645 +1914,672 @@
     </row>
     <row r="11" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F11" s="9"/>
+      <c r="G11">
+        <v>50</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G21">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F25" s="9"/>
-    </row>
-    <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="G25" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="28" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
         <v>72</v>
       </c>
-      <c r="E27" t="s">
+      <c r="B28" t="s">
         <v>72</v>
       </c>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" t="s">
-        <v>73</v>
-      </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
         <v>72</v>
       </c>
-      <c r="E29" t="s">
+      <c r="B30" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
         <v>72</v>
       </c>
-      <c r="E31" t="s">
+      <c r="B32" t="s">
         <v>72</v>
       </c>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
       <c r="D32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
     <row r="33" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
     <row r="35" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
+      <c r="G36">
+        <v>25</v>
+      </c>
     </row>
     <row r="37" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F37" s="9"/>
     </row>
     <row r="38" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
+      <c r="G38">
+        <v>23</v>
+      </c>
     </row>
     <row r="39" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
+      <c r="G40">
+        <v>21</v>
+      </c>
     </row>
     <row r="41" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="s">
         <v>67</v>
       </c>
-      <c r="C43" t="s">
-        <v>68</v>
-      </c>
       <c r="D43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" t="s">
         <v>67</v>
       </c>
-      <c r="C44" t="s">
-        <v>68</v>
-      </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
     <row r="45" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" t="s">
         <v>67</v>
       </c>
-      <c r="C45" t="s">
-        <v>68</v>
-      </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="9"/>
     </row>
     <row r="46" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" t="s">
         <v>67</v>
       </c>
-      <c r="C46" t="s">
-        <v>68</v>
-      </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
     <row r="47" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" t="s">
         <v>67</v>
       </c>
-      <c r="C47" t="s">
-        <v>68</v>
-      </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F47" s="9"/>
     </row>
     <row r="48" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
         <v>67</v>
       </c>
-      <c r="C48" t="s">
-        <v>68</v>
-      </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
     <row r="49" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" t="s">
         <v>67</v>
       </c>
-      <c r="C49" t="s">
-        <v>68</v>
-      </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
     <row r="51" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F51" s="9"/>
+      <c r="G51">
+        <v>10</v>
+      </c>
     </row>
     <row r="52" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
     </row>
     <row r="53" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F53" s="9"/>
     </row>
     <row r="54" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
     </row>
     <row r="55" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
     </row>
     <row r="57" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F57" s="9"/>
     </row>
     <row r="58" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
     </row>
     <row r="59" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F59" s="9"/>
     </row>
     <row r="60" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
@@ -2459,6 +2591,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F85234D-8D6A-4738-837D-AADE2DD4BDFB}">
+  <dimension ref="B2:N5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18">
+        <v>13</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" s="18">
+        <v>500000</v>
+      </c>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18">
+        <v>30</v>
+      </c>
+      <c r="J5" s="18">
+        <v>20000</v>
+      </c>
+      <c r="K5" s="18">
+        <v>100</v>
+      </c>
+      <c r="L5" s="18">
+        <v>11.5</v>
+      </c>
+      <c r="M5" s="18">
+        <v>20</v>
+      </c>
+      <c r="N5" s="18">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C330838-1509-4517-B74C-E85A6ACA858C}">
   <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -2481,16 +2695,16 @@
       </c>
       <c r="G1" s="3"/>
       <c r="I1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9"/>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+      <c r="B2">
+        <v>50</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2499,7 +2713,7 @@
       </c>
       <c r="G2"/>
       <c r="I2" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -2515,7 +2729,7 @@
       </c>
       <c r="E3"/>
       <c r="F3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3"/>
       <c r="H3" s="8">
@@ -2535,7 +2749,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="9"/>
       <c r="F4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="8">
@@ -2555,7 +2769,7 @@
       </c>
       <c r="E5"/>
       <c r="F5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5"/>
       <c r="H5" s="8">
@@ -2577,7 +2791,7 @@
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="8">
@@ -2597,7 +2811,7 @@
       </c>
       <c r="E7"/>
       <c r="F7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7"/>
       <c r="H7" s="8">
@@ -2607,15 +2821,15 @@
     <row r="8" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D8"/>
       <c r="E8" s="9"/>
       <c r="F8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8"/>
       <c r="H8" s="8">
@@ -2635,7 +2849,7 @@
       </c>
       <c r="E9"/>
       <c r="F9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="8">
@@ -2648,14 +2862,14 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D10">
         <v>35</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="8">
@@ -2677,7 +2891,7 @@
       </c>
       <c r="E11"/>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11"/>
       <c r="H11" s="8">
@@ -2690,14 +2904,14 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12">
         <v>34</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12"/>
       <c r="H12" s="8">
@@ -2717,7 +2931,7 @@
       </c>
       <c r="E13"/>
       <c r="F13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13"/>
       <c r="H13" s="8">
@@ -2737,7 +2951,7 @@
       <c r="D14"/>
       <c r="E14" s="9"/>
       <c r="F14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14"/>
       <c r="H14" s="8">
@@ -2747,17 +2961,17 @@
     <row r="15" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15"/>
       <c r="H15" s="8">
@@ -2777,7 +2991,7 @@
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16"/>
       <c r="H16" s="8">
@@ -2797,7 +3011,7 @@
       </c>
       <c r="E17"/>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17"/>
       <c r="H17" s="8">
@@ -2817,7 +3031,7 @@
       <c r="D18"/>
       <c r="E18" s="9"/>
       <c r="F18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18"/>
       <c r="H18" s="8">
@@ -2837,7 +3051,7 @@
       </c>
       <c r="E19"/>
       <c r="F19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19"/>
       <c r="H19" s="8">
@@ -2847,17 +3061,17 @@
     <row r="20" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20"/>
       <c r="H20" s="8">
@@ -2877,7 +3091,7 @@
       </c>
       <c r="E21"/>
       <c r="F21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G21"/>
       <c r="H21" s="8">
@@ -2897,7 +3111,7 @@
       <c r="D22"/>
       <c r="E22" s="9"/>
       <c r="F22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22"/>
       <c r="H22" s="8">
@@ -2917,7 +3131,7 @@
       </c>
       <c r="E23"/>
       <c r="F23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G23"/>
       <c r="H23" s="8">
@@ -2935,7 +3149,7 @@
       <c r="D24"/>
       <c r="E24" s="9"/>
       <c r="F24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24"/>
       <c r="H24" s="8">
@@ -2955,7 +3169,7 @@
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25"/>
       <c r="H25" s="8">
@@ -2975,7 +3189,7 @@
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26"/>
       <c r="H26" s="8">
@@ -2984,20 +3198,20 @@
     </row>
     <row r="27" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27"/>
       <c r="H27" s="8">
@@ -3017,7 +3231,7 @@
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G28"/>
       <c r="H28" s="8">
@@ -3039,7 +3253,7 @@
         <v>25.5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29"/>
       <c r="H29" s="8">
@@ -3059,7 +3273,7 @@
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30"/>
       <c r="H30" s="8">
@@ -3081,7 +3295,7 @@
         <v>24.5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G31"/>
       <c r="H31" s="8">
@@ -3101,7 +3315,7 @@
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G32"/>
       <c r="H32" s="8">
@@ -3110,20 +3324,20 @@
     </row>
     <row r="33" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G33"/>
       <c r="H33" s="8">
@@ -3145,7 +3359,7 @@
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G34"/>
       <c r="H34" s="8">
@@ -3165,7 +3379,7 @@
       </c>
       <c r="E35"/>
       <c r="F35" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G35"/>
       <c r="H35" s="8">
@@ -3183,7 +3397,7 @@
       <c r="D36"/>
       <c r="E36" s="9"/>
       <c r="F36" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G36"/>
       <c r="H36" s="8">
@@ -3203,7 +3417,7 @@
       </c>
       <c r="E37"/>
       <c r="F37" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G37"/>
       <c r="H37" s="8">
@@ -3213,15 +3427,15 @@
     <row r="38" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D38"/>
       <c r="E38" s="9"/>
       <c r="F38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G38"/>
       <c r="H38" s="8">
@@ -3241,7 +3455,7 @@
       </c>
       <c r="E39"/>
       <c r="F39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G39"/>
       <c r="H39" s="8">
@@ -3259,7 +3473,7 @@
       <c r="D40"/>
       <c r="E40" s="9"/>
       <c r="F40" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G40"/>
       <c r="H40" s="8">
@@ -3279,7 +3493,7 @@
       </c>
       <c r="E41"/>
       <c r="F41" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G41"/>
       <c r="H41" s="8">
@@ -3301,7 +3515,7 @@
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G42"/>
       <c r="H42" s="8">
@@ -3323,7 +3537,7 @@
         <v>18.5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G43"/>
       <c r="H43" s="8">
@@ -3336,14 +3550,14 @@
       </c>
       <c r="B44"/>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G44"/>
       <c r="H44" s="8">
@@ -3365,7 +3579,7 @@
         <v>17.5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G45"/>
       <c r="H45" s="8">
@@ -3385,7 +3599,7 @@
       </c>
       <c r="E46" s="9"/>
       <c r="F46" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G46"/>
       <c r="H46" s="8">
@@ -3401,13 +3615,13 @@
         <v>16.5</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E47">
         <v>16.5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G47"/>
       <c r="H47" s="8">
@@ -3427,7 +3641,7 @@
       </c>
       <c r="E48" s="9"/>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G48"/>
       <c r="H48" s="8">
@@ -3447,7 +3661,7 @@
       </c>
       <c r="E49"/>
       <c r="F49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G49"/>
       <c r="H49" s="8">
@@ -3457,15 +3671,15 @@
     <row r="50" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D50"/>
       <c r="E50" s="9"/>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50"/>
       <c r="H50" s="8">
@@ -3485,7 +3699,7 @@
       </c>
       <c r="E51"/>
       <c r="F51" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G51"/>
       <c r="H51" s="8">
@@ -3503,7 +3717,7 @@
       <c r="D52"/>
       <c r="E52" s="9"/>
       <c r="F52" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G52"/>
       <c r="H52" s="8">
@@ -3516,14 +3730,14 @@
         <v>13.5</v>
       </c>
       <c r="C53" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D53">
         <v>13.5</v>
       </c>
       <c r="E53"/>
       <c r="F53" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G53"/>
       <c r="H53" s="8">
@@ -3541,7 +3755,7 @@
       <c r="D54"/>
       <c r="E54" s="9"/>
       <c r="F54" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G54"/>
       <c r="H54" s="8">
@@ -3561,7 +3775,7 @@
       </c>
       <c r="E55"/>
       <c r="F55" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G55"/>
       <c r="H55" s="8">
@@ -3571,15 +3785,15 @@
     <row r="56" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D56"/>
       <c r="E56" s="9"/>
       <c r="F56" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G56"/>
       <c r="H56" s="8">
@@ -3599,7 +3813,7 @@
       </c>
       <c r="E57"/>
       <c r="F57" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G57"/>
       <c r="H57" s="8">
@@ -3617,7 +3831,7 @@
       <c r="D58"/>
       <c r="E58" s="9"/>
       <c r="F58" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G58"/>
       <c r="H58" s="8">
@@ -3630,14 +3844,14 @@
         <v>10.5</v>
       </c>
       <c r="C59" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D59">
         <v>10.5</v>
       </c>
       <c r="E59"/>
       <c r="F59" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G59"/>
       <c r="H59" s="8">
@@ -3655,7 +3869,7 @@
       <c r="D60"/>
       <c r="E60" s="9"/>
       <c r="F60" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G60"/>
       <c r="H60" s="8">
@@ -3677,1622 +3891,6 @@
       </c>
       <c r="E61" s="8">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2955AD-BE75-4102-9F56-068F093ACE7B}">
-  <dimension ref="A1:T62"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="L1" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="M1" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A2" s="19">
-        <v>0</v>
-      </c>
-      <c r="B2" s="19">
-        <v>10</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="18">
-        <v>9</v>
-      </c>
-      <c r="E2" s="18">
-        <v>100</v>
-      </c>
-      <c r="F2" s="18">
-        <v>3</v>
-      </c>
-      <c r="G2" s="18">
-        <v>6</v>
-      </c>
-      <c r="H2" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="I2" s="18">
-        <v>4</v>
-      </c>
-      <c r="J2" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="K2" s="18">
-        <v>1</v>
-      </c>
-      <c r="L2" s="18">
-        <v>5</v>
-      </c>
-      <c r="M2" s="18">
-        <v>0</v>
-      </c>
-      <c r="N2" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="P2" s="18">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A3" s="18">
-        <v>1</v>
-      </c>
-      <c r="B3" s="18">
-        <v>11</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="18">
-        <v>4</v>
-      </c>
-      <c r="E3" s="18">
-        <v>200</v>
-      </c>
-      <c r="F3" s="18">
-        <v>2.5</v>
-      </c>
-      <c r="G3" s="18">
-        <v>4.5</v>
-      </c>
-      <c r="H3" s="18">
-        <v>0.45</v>
-      </c>
-      <c r="I3" s="18">
-        <v>6</v>
-      </c>
-      <c r="J3" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="K3" s="18">
-        <v>1</v>
-      </c>
-      <c r="L3" s="18">
-        <v>10</v>
-      </c>
-      <c r="M3" s="18">
-        <v>0</v>
-      </c>
-      <c r="N3" s="18">
-        <v>0.75</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="P3" s="18">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <f>MOD(R3,9)</f>
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <f>MOD(R3+3,8)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A4" s="18">
-        <v>2</v>
-      </c>
-      <c r="B4" s="18">
-        <v>12</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="18">
-        <v>8</v>
-      </c>
-      <c r="E4" s="18">
-        <v>300</v>
-      </c>
-      <c r="F4" s="18">
-        <v>1.6</v>
-      </c>
-      <c r="G4" s="18">
-        <v>6</v>
-      </c>
-      <c r="H4" s="18">
-        <v>0.4</v>
-      </c>
-      <c r="I4" s="18">
-        <v>6</v>
-      </c>
-      <c r="J4" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="K4" s="18">
-        <v>1</v>
-      </c>
-      <c r="L4" s="18">
-        <v>45</v>
-      </c>
-      <c r="M4" s="18">
-        <v>50</v>
-      </c>
-      <c r="N4" s="18">
-        <v>1</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="P4" s="18">
-        <v>2</v>
-      </c>
-      <c r="R4">
-        <v>2</v>
-      </c>
-      <c r="S4">
-        <f>MOD(R4,9)</f>
-        <v>2</v>
-      </c>
-      <c r="T4">
-        <f t="shared" ref="T4:T32" si="0">MOD(R4+3,8)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A5" s="18">
-        <v>3</v>
-      </c>
-      <c r="B5" s="18">
-        <v>13</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="18">
-        <v>3</v>
-      </c>
-      <c r="E5" s="18">
-        <v>400</v>
-      </c>
-      <c r="F5" s="18">
-        <v>1</v>
-      </c>
-      <c r="G5" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="I5" s="18">
-        <v>8</v>
-      </c>
-      <c r="J5" s="18">
-        <v>1</v>
-      </c>
-      <c r="K5" s="18">
-        <v>1</v>
-      </c>
-      <c r="L5" s="18">
-        <v>15</v>
-      </c>
-      <c r="M5" s="18">
-        <v>50</v>
-      </c>
-      <c r="N5" s="18">
-        <v>1</v>
-      </c>
-      <c r="O5" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="P5" s="18">
-        <v>3</v>
-      </c>
-      <c r="R5">
-        <v>3</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S62" si="1">MOD(R5,9)</f>
-        <v>3</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A6" s="18">
-        <v>4</v>
-      </c>
-      <c r="B6" s="18">
-        <v>14</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="18">
-        <v>8</v>
-      </c>
-      <c r="E6" s="18">
-        <v>400</v>
-      </c>
-      <c r="F6" s="18">
-        <v>10</v>
-      </c>
-      <c r="G6" s="18">
-        <v>0.8</v>
-      </c>
-      <c r="H6" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="I6" s="18">
-        <v>4</v>
-      </c>
-      <c r="J6" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="K6" s="18">
-        <v>1</v>
-      </c>
-      <c r="L6" s="18">
-        <v>35</v>
-      </c>
-      <c r="M6" s="18">
-        <v>0</v>
-      </c>
-      <c r="N6" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="O6" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="P6" s="18">
-        <v>2</v>
-      </c>
-      <c r="R6">
-        <v>4</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A7" s="18">
-        <v>5</v>
-      </c>
-      <c r="B7" s="18">
-        <v>15</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="18">
-        <v>6</v>
-      </c>
-      <c r="E7" s="18">
-        <v>500</v>
-      </c>
-      <c r="F7" s="18">
-        <v>8</v>
-      </c>
-      <c r="G7" s="18">
-        <v>1</v>
-      </c>
-      <c r="H7" s="18">
-        <v>0.35</v>
-      </c>
-      <c r="I7" s="18">
-        <v>6</v>
-      </c>
-      <c r="J7" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="K7" s="18">
-        <v>1</v>
-      </c>
-      <c r="L7" s="18">
-        <v>55</v>
-      </c>
-      <c r="M7" s="18">
-        <v>50</v>
-      </c>
-      <c r="N7" s="18">
-        <v>0.75</v>
-      </c>
-      <c r="O7" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="P7" s="18">
-        <v>3</v>
-      </c>
-      <c r="R7">
-        <v>5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A8" s="18">
-        <v>6</v>
-      </c>
-      <c r="B8" s="18">
-        <v>16</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="18">
-        <v>6</v>
-      </c>
-      <c r="E8" s="18">
-        <v>600</v>
-      </c>
-      <c r="F8" s="18">
-        <v>7</v>
-      </c>
-      <c r="G8" s="18">
-        <v>0.9</v>
-      </c>
-      <c r="H8" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="18">
-        <v>8</v>
-      </c>
-      <c r="J8" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="K8" s="18">
-        <v>1</v>
-      </c>
-      <c r="L8" s="18">
-        <v>75</v>
-      </c>
-      <c r="M8" s="18">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18">
-        <v>0.75</v>
-      </c>
-      <c r="O8" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="P8" s="18">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>6</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A9" s="18">
-        <v>7</v>
-      </c>
-      <c r="B9" s="18">
-        <v>17</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="18">
-        <v>3</v>
-      </c>
-      <c r="E9" s="18">
-        <v>800</v>
-      </c>
-      <c r="F9" s="18">
-        <v>6</v>
-      </c>
-      <c r="G9" s="18">
-        <v>1.25</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0.35</v>
-      </c>
-      <c r="I9" s="18">
-        <v>8</v>
-      </c>
-      <c r="J9" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="18">
-        <v>1</v>
-      </c>
-      <c r="L9" s="18">
-        <v>110</v>
-      </c>
-      <c r="M9" s="18">
-        <v>50</v>
-      </c>
-      <c r="N9" s="18">
-        <v>1</v>
-      </c>
-      <c r="O9" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="P9" s="18">
-        <v>2</v>
-      </c>
-      <c r="R9">
-        <v>7</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A10" s="18">
-        <v>8</v>
-      </c>
-      <c r="B10" s="18">
-        <v>18</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="18">
-        <v>1</v>
-      </c>
-      <c r="E10" s="18">
-        <v>2000</v>
-      </c>
-      <c r="F10" s="18">
-        <v>2</v>
-      </c>
-      <c r="G10" s="18">
-        <v>3.6</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0.6</v>
-      </c>
-      <c r="I10" s="18">
-        <v>4</v>
-      </c>
-      <c r="J10" s="18">
-        <v>1</v>
-      </c>
-      <c r="K10" s="18">
-        <v>1</v>
-      </c>
-      <c r="L10" s="18">
-        <v>110</v>
-      </c>
-      <c r="M10" s="18">
-        <v>50</v>
-      </c>
-      <c r="N10" s="18">
-        <v>1.25</v>
-      </c>
-      <c r="O10" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="P10" s="18">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>8</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R11">
-        <v>9</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>103</v>
-      </c>
-      <c r="R12">
-        <v>10</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R13">
-        <v>11</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>104</v>
-      </c>
-      <c r="R14">
-        <v>12</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>105</v>
-      </c>
-      <c r="R15">
-        <v>13</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>117</v>
-      </c>
-      <c r="R16">
-        <v>14</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R17">
-        <v>15</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>118</v>
-      </c>
-      <c r="R18">
-        <v>16</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R19">
-        <v>17</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>119</v>
-      </c>
-      <c r="R20">
-        <v>18</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="R21">
-        <v>19</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R22">
-        <v>20</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>121</v>
-      </c>
-      <c r="R23">
-        <v>21</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>126</v>
-      </c>
-      <c r="R24">
-        <v>22</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T24">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>120</v>
-      </c>
-      <c r="R25">
-        <v>23</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="T25">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>123</v>
-      </c>
-      <c r="R26">
-        <v>24</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="T26">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R27">
-        <v>25</v>
-      </c>
-      <c r="S27">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="T27">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>124</v>
-      </c>
-      <c r="R28">
-        <v>26</v>
-      </c>
-      <c r="S28">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="T28">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R29">
-        <v>27</v>
-      </c>
-      <c r="S29">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>125</v>
-      </c>
-      <c r="R30">
-        <v>28</v>
-      </c>
-      <c r="S30">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T30">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A31" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="K31" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="L31" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="M31" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="R31">
-        <v>29</v>
-      </c>
-      <c r="S31">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="T31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18">
-        <v>10</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="18">
-        <v>100000</v>
-      </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18">
-        <v>24</v>
-      </c>
-      <c r="I32" s="18">
-        <v>18000</v>
-      </c>
-      <c r="J32" s="18">
-        <v>100</v>
-      </c>
-      <c r="K32" s="18">
-        <v>10</v>
-      </c>
-      <c r="L32" s="18">
-        <v>10</v>
-      </c>
-      <c r="M32" s="18">
-        <v>5</v>
-      </c>
-      <c r="R32">
-        <v>30</v>
-      </c>
-      <c r="S32">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="T32">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18">
-        <v>11</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="18">
-        <v>110000</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18">
-        <v>25</v>
-      </c>
-      <c r="I33" s="18">
-        <v>20000</v>
-      </c>
-      <c r="J33" s="18">
-        <v>100</v>
-      </c>
-      <c r="K33" s="18">
-        <v>10.5</v>
-      </c>
-      <c r="L33" s="18">
-        <v>20</v>
-      </c>
-      <c r="M33" s="18">
-        <v>10</v>
-      </c>
-      <c r="R33">
-        <v>31</v>
-      </c>
-      <c r="S33">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T33">
-        <f t="shared" ref="T33:T62" si="2">MOD(R33+3,8)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18">
-        <v>12</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="18">
-        <v>120000</v>
-      </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18">
-        <v>26</v>
-      </c>
-      <c r="I34" s="18">
-        <v>20000</v>
-      </c>
-      <c r="J34" s="18">
-        <v>100</v>
-      </c>
-      <c r="K34" s="18">
-        <v>11</v>
-      </c>
-      <c r="L34" s="18">
-        <v>20</v>
-      </c>
-      <c r="M34" s="18">
-        <v>10</v>
-      </c>
-      <c r="R34">
-        <v>32</v>
-      </c>
-      <c r="S34">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="T34">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18">
-        <v>13</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="18">
-        <v>130000</v>
-      </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18">
-        <v>27</v>
-      </c>
-      <c r="I35" s="18">
-        <v>20000</v>
-      </c>
-      <c r="J35" s="18">
-        <v>100</v>
-      </c>
-      <c r="K35" s="18">
-        <v>11.5</v>
-      </c>
-      <c r="L35" s="18">
-        <v>20</v>
-      </c>
-      <c r="M35" s="18">
-        <v>10</v>
-      </c>
-      <c r="R35">
-        <v>33</v>
-      </c>
-      <c r="S35">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18">
-        <v>20</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="18">
-        <v>200000</v>
-      </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18">
-        <v>34</v>
-      </c>
-      <c r="I36" s="18">
-        <v>20000</v>
-      </c>
-      <c r="J36" s="18">
-        <v>100</v>
-      </c>
-      <c r="K36" s="18">
-        <v>15</v>
-      </c>
-      <c r="L36" s="18">
-        <v>30</v>
-      </c>
-      <c r="M36" s="18">
-        <v>20</v>
-      </c>
-      <c r="R36">
-        <v>34</v>
-      </c>
-      <c r="S36">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="T36">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18">
-        <v>30</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="18">
-        <v>300000</v>
-      </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18">
-        <v>44</v>
-      </c>
-      <c r="I37" s="18">
-        <v>20000</v>
-      </c>
-      <c r="J37" s="18">
-        <v>100</v>
-      </c>
-      <c r="K37" s="18">
-        <v>20</v>
-      </c>
-      <c r="L37" s="18">
-        <v>40</v>
-      </c>
-      <c r="M37" s="18">
-        <v>30</v>
-      </c>
-      <c r="R37">
-        <v>35</v>
-      </c>
-      <c r="S37">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="T37">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18">
-        <v>40</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" s="18">
-        <v>400000</v>
-      </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18">
-        <v>54</v>
-      </c>
-      <c r="I38" s="18">
-        <v>20000</v>
-      </c>
-      <c r="J38" s="18">
-        <v>100</v>
-      </c>
-      <c r="K38" s="18">
-        <v>25</v>
-      </c>
-      <c r="L38" s="18">
-        <v>50</v>
-      </c>
-      <c r="M38" s="18">
-        <v>40</v>
-      </c>
-      <c r="R38">
-        <v>36</v>
-      </c>
-      <c r="S38">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18">
-        <v>50</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="18">
-        <v>500000</v>
-      </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18">
-        <v>64</v>
-      </c>
-      <c r="I39" s="18">
-        <v>20000</v>
-      </c>
-      <c r="J39" s="18">
-        <v>100</v>
-      </c>
-      <c r="K39" s="18">
-        <v>30</v>
-      </c>
-      <c r="L39" s="18">
-        <v>60</v>
-      </c>
-      <c r="M39" s="18">
-        <v>50</v>
-      </c>
-      <c r="R39">
-        <v>37</v>
-      </c>
-      <c r="S39">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T39">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="R40">
-        <v>38</v>
-      </c>
-      <c r="S40">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="T40">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>140</v>
-      </c>
-      <c r="R41">
-        <v>39</v>
-      </c>
-      <c r="S41">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="T41">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
-        <v>141</v>
-      </c>
-      <c r="R42">
-        <v>40</v>
-      </c>
-      <c r="S42">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T42">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A44" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="B44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A45">
-        <v>2</v>
-      </c>
-      <c r="B45" t="s">
-        <v>142</v>
-      </c>
-      <c r="R45">
-        <v>43</v>
-      </c>
-      <c r="S45">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="T45">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A46">
-        <v>3</v>
-      </c>
-      <c r="B46" t="s">
-        <v>143</v>
-      </c>
-      <c r="R46">
-        <v>44</v>
-      </c>
-      <c r="S46">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="T46">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A47">
-        <v>4</v>
-      </c>
-      <c r="B47" t="s">
-        <v>144</v>
-      </c>
-      <c r="R47">
-        <v>45</v>
-      </c>
-      <c r="S47">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A48">
-        <v>5</v>
-      </c>
-      <c r="B48" t="s">
-        <v>146</v>
-      </c>
-      <c r="R48">
-        <v>46</v>
-      </c>
-      <c r="S48">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T48">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R49">
-        <v>47</v>
-      </c>
-      <c r="S49">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="T49">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R50">
-        <v>48</v>
-      </c>
-      <c r="S50">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="T50">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R51">
-        <v>49</v>
-      </c>
-      <c r="S51">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T51">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R52">
-        <v>50</v>
-      </c>
-      <c r="S52">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="T52">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R53">
-        <v>51</v>
-      </c>
-      <c r="S53">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="T53">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R54">
-        <v>52</v>
-      </c>
-      <c r="S54">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="T54">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R55">
-        <v>53</v>
-      </c>
-      <c r="S55">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="T55">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R56">
-        <v>54</v>
-      </c>
-      <c r="S56">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R57">
-        <v>55</v>
-      </c>
-      <c r="S57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T57">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R58">
-        <v>56</v>
-      </c>
-      <c r="S58">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="T58">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R59">
-        <v>57</v>
-      </c>
-      <c r="S59">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="T59">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R60">
-        <v>58</v>
-      </c>
-      <c r="S60">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T60">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R61">
-        <v>59</v>
-      </c>
-      <c r="S61">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="T61">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="18:20" x14ac:dyDescent="0.4">
-      <c r="R62">
-        <v>60</v>
-      </c>
-      <c r="S62">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="T62">
-        <f t="shared" si="2"/>
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5302,6 +3900,1622 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A2955AD-BE75-4102-9F56-068F093ACE7B}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A1" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A2" s="19">
+        <v>0</v>
+      </c>
+      <c r="B2" s="19">
+        <v>10</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="18">
+        <v>9</v>
+      </c>
+      <c r="E2" s="18">
+        <v>100</v>
+      </c>
+      <c r="F2" s="18">
+        <v>3</v>
+      </c>
+      <c r="G2" s="18">
+        <v>6</v>
+      </c>
+      <c r="H2" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="18">
+        <v>4</v>
+      </c>
+      <c r="J2" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K2" s="18">
+        <v>1</v>
+      </c>
+      <c r="L2" s="18">
+        <v>5</v>
+      </c>
+      <c r="M2" s="18">
+        <v>0</v>
+      </c>
+      <c r="N2" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="P2" s="18">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A3" s="18">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18">
+        <v>11</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="18">
+        <v>4</v>
+      </c>
+      <c r="E3" s="18">
+        <v>200</v>
+      </c>
+      <c r="F3" s="18">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="18">
+        <v>0.45</v>
+      </c>
+      <c r="I3" s="18">
+        <v>6</v>
+      </c>
+      <c r="J3" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="18">
+        <v>1</v>
+      </c>
+      <c r="L3" s="18">
+        <v>10</v>
+      </c>
+      <c r="M3" s="18">
+        <v>0</v>
+      </c>
+      <c r="N3" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="P3" s="18">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <f>MOD(R3,9)</f>
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <f>MOD(R3+3,8)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18">
+        <v>12</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="18">
+        <v>8</v>
+      </c>
+      <c r="E4" s="18">
+        <v>300</v>
+      </c>
+      <c r="F4" s="18">
+        <v>1.6</v>
+      </c>
+      <c r="G4" s="18">
+        <v>6</v>
+      </c>
+      <c r="H4" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="I4" s="18">
+        <v>6</v>
+      </c>
+      <c r="J4" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="18">
+        <v>1</v>
+      </c>
+      <c r="L4" s="18">
+        <v>45</v>
+      </c>
+      <c r="M4" s="18">
+        <v>50</v>
+      </c>
+      <c r="N4" s="18">
+        <v>1</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="P4" s="18">
+        <v>2</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <f>MOD(R4,9)</f>
+        <v>2</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T32" si="0">MOD(R4+3,8)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A5" s="18">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18">
+        <v>13</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="18">
+        <v>3</v>
+      </c>
+      <c r="E5" s="18">
+        <v>400</v>
+      </c>
+      <c r="F5" s="18">
+        <v>1</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="18">
+        <v>8</v>
+      </c>
+      <c r="J5" s="18">
+        <v>1</v>
+      </c>
+      <c r="K5" s="18">
+        <v>1</v>
+      </c>
+      <c r="L5" s="18">
+        <v>15</v>
+      </c>
+      <c r="M5" s="18">
+        <v>50</v>
+      </c>
+      <c r="N5" s="18">
+        <v>1</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" s="18">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S62" si="1">MOD(R5,9)</f>
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A6" s="18">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18">
+        <v>14</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="18">
+        <v>8</v>
+      </c>
+      <c r="E6" s="18">
+        <v>400</v>
+      </c>
+      <c r="F6" s="18">
+        <v>10</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="I6" s="18">
+        <v>4</v>
+      </c>
+      <c r="J6" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="18">
+        <v>1</v>
+      </c>
+      <c r="L6" s="18">
+        <v>35</v>
+      </c>
+      <c r="M6" s="18">
+        <v>0</v>
+      </c>
+      <c r="N6" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="P6" s="18">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>4</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A7" s="18">
+        <v>5</v>
+      </c>
+      <c r="B7" s="18">
+        <v>15</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="18">
+        <v>6</v>
+      </c>
+      <c r="E7" s="18">
+        <v>500</v>
+      </c>
+      <c r="F7" s="18">
+        <v>8</v>
+      </c>
+      <c r="G7" s="18">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.35</v>
+      </c>
+      <c r="I7" s="18">
+        <v>6</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="18">
+        <v>1</v>
+      </c>
+      <c r="L7" s="18">
+        <v>55</v>
+      </c>
+      <c r="M7" s="18">
+        <v>50</v>
+      </c>
+      <c r="N7" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="O7" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="P7" s="18">
+        <v>3</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A8" s="18">
+        <v>6</v>
+      </c>
+      <c r="B8" s="18">
+        <v>16</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="18">
+        <v>6</v>
+      </c>
+      <c r="E8" s="18">
+        <v>600</v>
+      </c>
+      <c r="F8" s="18">
+        <v>7</v>
+      </c>
+      <c r="G8" s="18">
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="18">
+        <v>8</v>
+      </c>
+      <c r="J8" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="18">
+        <v>1</v>
+      </c>
+      <c r="L8" s="18">
+        <v>75</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0</v>
+      </c>
+      <c r="N8" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="O8" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="P8" s="18">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>6</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A9" s="18">
+        <v>7</v>
+      </c>
+      <c r="B9" s="18">
+        <v>17</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="18">
+        <v>3</v>
+      </c>
+      <c r="E9" s="18">
+        <v>800</v>
+      </c>
+      <c r="F9" s="18">
+        <v>6</v>
+      </c>
+      <c r="G9" s="18">
+        <v>1.25</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0.35</v>
+      </c>
+      <c r="I9" s="18">
+        <v>8</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="18">
+        <v>1</v>
+      </c>
+      <c r="L9" s="18">
+        <v>110</v>
+      </c>
+      <c r="M9" s="18">
+        <v>50</v>
+      </c>
+      <c r="N9" s="18">
+        <v>1</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="P9" s="18">
+        <v>2</v>
+      </c>
+      <c r="R9">
+        <v>7</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A10" s="18">
+        <v>8</v>
+      </c>
+      <c r="B10" s="18">
+        <v>18</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="18">
+        <v>1</v>
+      </c>
+      <c r="E10" s="18">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="18">
+        <v>2</v>
+      </c>
+      <c r="G10" s="18">
+        <v>3.6</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0.6</v>
+      </c>
+      <c r="I10" s="18">
+        <v>4</v>
+      </c>
+      <c r="J10" s="18">
+        <v>1</v>
+      </c>
+      <c r="K10" s="18">
+        <v>1</v>
+      </c>
+      <c r="L10" s="18">
+        <v>110</v>
+      </c>
+      <c r="M10" s="18">
+        <v>50</v>
+      </c>
+      <c r="N10" s="18">
+        <v>1.25</v>
+      </c>
+      <c r="O10" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="P10" s="18">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>8</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R11">
+        <v>9</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>102</v>
+      </c>
+      <c r="R12">
+        <v>10</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R13">
+        <v>11</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>103</v>
+      </c>
+      <c r="R14">
+        <v>12</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>104</v>
+      </c>
+      <c r="R15">
+        <v>13</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>116</v>
+      </c>
+      <c r="R16">
+        <v>14</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R17">
+        <v>15</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+      <c r="R18">
+        <v>16</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R19">
+        <v>17</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>118</v>
+      </c>
+      <c r="R20">
+        <v>18</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="R21">
+        <v>19</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R22">
+        <v>20</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="R23">
+        <v>21</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>125</v>
+      </c>
+      <c r="R24">
+        <v>22</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="R25">
+        <v>23</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="R26">
+        <v>24</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R27">
+        <v>25</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>123</v>
+      </c>
+      <c r="R28">
+        <v>26</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R29">
+        <v>27</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>124</v>
+      </c>
+      <c r="R30">
+        <v>28</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A31" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="R31">
+        <v>29</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18">
+        <v>10</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="18">
+        <v>100000</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18">
+        <v>24</v>
+      </c>
+      <c r="I32" s="18">
+        <v>18000</v>
+      </c>
+      <c r="J32" s="18">
+        <v>100</v>
+      </c>
+      <c r="K32" s="18">
+        <v>10</v>
+      </c>
+      <c r="L32" s="18">
+        <v>10</v>
+      </c>
+      <c r="M32" s="18">
+        <v>5</v>
+      </c>
+      <c r="R32">
+        <v>30</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18">
+        <v>11</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="18">
+        <v>110000</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18">
+        <v>25</v>
+      </c>
+      <c r="I33" s="18">
+        <v>20000</v>
+      </c>
+      <c r="J33" s="18">
+        <v>100</v>
+      </c>
+      <c r="K33" s="18">
+        <v>10.5</v>
+      </c>
+      <c r="L33" s="18">
+        <v>20</v>
+      </c>
+      <c r="M33" s="18">
+        <v>10</v>
+      </c>
+      <c r="R33">
+        <v>31</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T33">
+        <f t="shared" ref="T33:T62" si="2">MOD(R33+3,8)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18">
+        <v>12</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="18">
+        <v>120000</v>
+      </c>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18">
+        <v>26</v>
+      </c>
+      <c r="I34" s="18">
+        <v>20000</v>
+      </c>
+      <c r="J34" s="18">
+        <v>100</v>
+      </c>
+      <c r="K34" s="18">
+        <v>11</v>
+      </c>
+      <c r="L34" s="18">
+        <v>20</v>
+      </c>
+      <c r="M34" s="18">
+        <v>10</v>
+      </c>
+      <c r="R34">
+        <v>32</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18">
+        <v>13</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" s="18">
+        <v>130000</v>
+      </c>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18">
+        <v>27</v>
+      </c>
+      <c r="I35" s="18">
+        <v>20000</v>
+      </c>
+      <c r="J35" s="18">
+        <v>100</v>
+      </c>
+      <c r="K35" s="18">
+        <v>11.5</v>
+      </c>
+      <c r="L35" s="18">
+        <v>20</v>
+      </c>
+      <c r="M35" s="18">
+        <v>10</v>
+      </c>
+      <c r="R35">
+        <v>33</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18">
+        <v>20</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="18">
+        <v>200000</v>
+      </c>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18">
+        <v>34</v>
+      </c>
+      <c r="I36" s="18">
+        <v>20000</v>
+      </c>
+      <c r="J36" s="18">
+        <v>100</v>
+      </c>
+      <c r="K36" s="18">
+        <v>15</v>
+      </c>
+      <c r="L36" s="18">
+        <v>30</v>
+      </c>
+      <c r="M36" s="18">
+        <v>20</v>
+      </c>
+      <c r="R36">
+        <v>34</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18">
+        <v>30</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="18">
+        <v>300000</v>
+      </c>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18">
+        <v>44</v>
+      </c>
+      <c r="I37" s="18">
+        <v>20000</v>
+      </c>
+      <c r="J37" s="18">
+        <v>100</v>
+      </c>
+      <c r="K37" s="18">
+        <v>20</v>
+      </c>
+      <c r="L37" s="18">
+        <v>40</v>
+      </c>
+      <c r="M37" s="18">
+        <v>30</v>
+      </c>
+      <c r="R37">
+        <v>35</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18">
+        <v>40</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="18">
+        <v>400000</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18">
+        <v>54</v>
+      </c>
+      <c r="I38" s="18">
+        <v>20000</v>
+      </c>
+      <c r="J38" s="18">
+        <v>100</v>
+      </c>
+      <c r="K38" s="18">
+        <v>25</v>
+      </c>
+      <c r="L38" s="18">
+        <v>50</v>
+      </c>
+      <c r="M38" s="18">
+        <v>40</v>
+      </c>
+      <c r="R38">
+        <v>36</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18">
+        <v>50</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="18">
+        <v>500000</v>
+      </c>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18">
+        <v>64</v>
+      </c>
+      <c r="I39" s="18">
+        <v>20000</v>
+      </c>
+      <c r="J39" s="18">
+        <v>100</v>
+      </c>
+      <c r="K39" s="18">
+        <v>30</v>
+      </c>
+      <c r="L39" s="18">
+        <v>60</v>
+      </c>
+      <c r="M39" s="18">
+        <v>50</v>
+      </c>
+      <c r="R39">
+        <v>37</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="R40">
+        <v>38</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>139</v>
+      </c>
+      <c r="R41">
+        <v>39</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>140</v>
+      </c>
+      <c r="R42">
+        <v>40</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A44" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>2</v>
+      </c>
+      <c r="B45" t="s">
+        <v>141</v>
+      </c>
+      <c r="R45">
+        <v>43</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="R46">
+        <v>44</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>143</v>
+      </c>
+      <c r="R47">
+        <v>45</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>145</v>
+      </c>
+      <c r="R48">
+        <v>46</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R49">
+        <v>47</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R50">
+        <v>48</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R51">
+        <v>49</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R52">
+        <v>50</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R53">
+        <v>51</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R54">
+        <v>52</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R55">
+        <v>53</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R56">
+        <v>54</v>
+      </c>
+      <c r="S56">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R57">
+        <v>55</v>
+      </c>
+      <c r="S57">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T57">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R58">
+        <v>56</v>
+      </c>
+      <c r="S58">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T58">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R59">
+        <v>57</v>
+      </c>
+      <c r="S59">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="T59">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R60">
+        <v>58</v>
+      </c>
+      <c r="S60">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T60">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R61">
+        <v>59</v>
+      </c>
+      <c r="S61">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T61">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="18:20" x14ac:dyDescent="0.4">
+      <c r="R62">
+        <v>60</v>
+      </c>
+      <c r="S62">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="T62">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C49FFA-D35B-4AF1-B8C1-B7B935FDDD03}">
   <dimension ref="A1:O60"/>
   <sheetFormatPr defaultColWidth="4.5" defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -6856,258 +7070,6 @@
     </row>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
@@ -7126,8 +7088,412 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:I60"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6211F03-087E-45DF-8A63-3BB505890CC6}">
+  <dimension ref="B2:C20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/public/files/MAP/MAP002.xlsx
+++ b/public/files/MAP/MAP002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\MAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29024339-52A9-4892-B016-6184B7687BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DB4BF1-4135-4B0F-AF52-E9E36B059071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="750" windowWidth="26205" windowHeight="14850" activeTab="5" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
+    <workbookView xWindow="450" yWindow="630" windowWidth="26205" windowHeight="14850" activeTab="2" xr2:uid="{38351AC5-F874-4B4A-BA41-290077078325}"/>
   </bookViews>
   <sheets>
     <sheet name="MAP" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="190">
   <si>
     <t>##このページは人間が確認するための疑似ヘクスマップ</t>
     <rPh sb="8" eb="10">
@@ -352,41 +352,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>タワーではヘクスごとに2ウェーブの戦闘を行う。</t>
-    <rPh sb="17" eb="19">
-      <t>セントウ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出現するタイプが2種類、合計出現数が決まっていて、どちらがどれだけ出てくるかはランダム</t>
-    <rPh sb="0" eb="2">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>シュ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ルイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ゴウケイ</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>シュツゲンスウ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>デ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1f</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -987,104 +952,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>12,魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>15、魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>10.5、魔女</t>
-    <rPh sb="5" eb="7">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>13.5、魔女</t>
-    <rPh sb="5" eb="7">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>16.5、魔女</t>
-    <rPh sb="5" eb="7">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>18、魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>21、魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>23.5、魔女</t>
-    <rPh sb="5" eb="7">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>26.5、魔女</t>
-    <rPh sb="5" eb="7">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>30、魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>32.5、魔女</t>
-    <rPh sb="5" eb="7">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>34、魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>35、魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>36、魔女</t>
-    <rPh sb="3" eb="5">
-      <t>マジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>白</t>
     <rPh sb="0" eb="1">
       <t>シロ</t>
@@ -1197,6 +1064,64 @@
   </si>
   <si>
     <t>プロセル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11,魔女</t>
+  </si>
+  <si>
+    <t>top of tower</t>
+  </si>
+  <si>
+    <t>62,魔女</t>
+  </si>
+  <si>
+    <t>60,魔女</t>
+  </si>
+  <si>
+    <t>58,魔女</t>
+  </si>
+  <si>
+    <t>55,魔女</t>
+  </si>
+  <si>
+    <t>50,魔女</t>
+  </si>
+  <si>
+    <t>43,魔女</t>
+  </si>
+  <si>
+    <t>37,魔女</t>
+  </si>
+  <si>
+    <t>32,魔女</t>
+  </si>
+  <si>
+    <t>26,魔女</t>
+  </si>
+  <si>
+    <t>23,魔女</t>
+  </si>
+  <si>
+    <t>20,魔女</t>
+  </si>
+  <si>
+    <t>17,魔女</t>
+  </si>
+  <si>
+    <t>14,魔女</t>
+  </si>
+  <si>
+    <t>2f</t>
+  </si>
+  <si>
+    <t>1f</t>
+  </si>
+  <si>
+    <t>こっちはコピペ用。</t>
+    <rPh sb="7" eb="8">
+      <t>ヨウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1427,11 +1352,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1765,10 +1690,10 @@
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9"/>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1787,7 +1712,7 @@
       </c>
       <c r="F3" s="9"/>
       <c r="H3" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K3" s="3"/>
     </row>
@@ -1806,7 +1731,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -1823,7 +1748,7 @@
       </c>
       <c r="F5" s="9"/>
       <c r="H5" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -1843,7 +1768,7 @@
       <c r="F6" s="9"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I6" s="3"/>
     </row>
@@ -1859,10 +1784,10 @@
       </c>
       <c r="F7" s="9"/>
       <c r="H7" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -1875,7 +1800,7 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="I8" s="3"/>
     </row>
@@ -1887,7 +1812,7 @@
         <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="3">
@@ -1914,7 +1839,7 @@
     </row>
     <row r="11" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
         <v>75</v>
@@ -1940,7 +1865,7 @@
         <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
@@ -1959,7 +1884,7 @@
     </row>
     <row r="14" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
         <v>75</v>
@@ -1990,7 +1915,7 @@
         <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
@@ -2009,7 +1934,7 @@
     </row>
     <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
@@ -2040,7 +1965,7 @@
         <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
@@ -2062,7 +1987,7 @@
     </row>
     <row r="22" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
         <v>74</v>
@@ -2095,7 +2020,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -2110,7 +2035,7 @@
       </c>
       <c r="F25" s="9"/>
       <c r="G25" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
@@ -2597,40 +2522,40 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B4" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F4" s="18"/>
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="K4" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="L4" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="K4" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>96</v>
-      </c>
       <c r="M4" s="18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
@@ -2639,7 +2564,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E5" s="18">
         <v>500000</v>
@@ -2674,19 +2599,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C330838-1509-4517-B74C-E85A6ACA858C}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="5" width="9" style="8"/>
     <col min="6" max="6" width="9" style="17"/>
-    <col min="7" max="16384" width="9" style="8"/>
+    <col min="7" max="15" width="9" style="8"/>
+    <col min="16" max="16" width="9" style="17"/>
+    <col min="17" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="3" t="s">
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
@@ -2694,17 +2621,27 @@
         <v>2</v>
       </c>
       <c r="G1" s="3"/>
-      <c r="I1" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9"/>
       <c r="B2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2712,20 +2649,29 @@
         <v>3</v>
       </c>
       <c r="G2"/>
-      <c r="I2" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K2" s="9"/>
+      <c r="L2">
+        <v>80</v>
+      </c>
+      <c r="M2">
+        <v>80</v>
+      </c>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3"/>
       <c r="B3">
-        <v>38.5</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>38.5</v>
+        <v>67</v>
       </c>
       <c r="D3">
-        <v>38.5</v>
+        <v>67</v>
       </c>
       <c r="E3"/>
       <c r="F3" s="2" t="s">
@@ -2733,18 +2679,38 @@
       </c>
       <c r="G3"/>
       <c r="H3" s="8">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>67</v>
+      </c>
+      <c r="K3"/>
+      <c r="L3">
+        <f t="shared" ref="L3:N3" si="0">$R3</f>
+        <v>67</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="O3"/>
+      <c r="P3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="B4">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="9"/>
@@ -2753,19 +2719,39 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="8">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:M4" si="1">$R4</f>
+        <v>66</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R4" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5"/>
       <c r="B5">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="D5">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="2" t="s">
@@ -2773,21 +2759,41 @@
       </c>
       <c r="G5"/>
       <c r="H5" s="8">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5">
+        <f t="shared" ref="L5:N5" si="2">$R5</f>
+        <v>65</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="B6">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="2" t="s">
@@ -2795,19 +2801,42 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="8">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ref="K6:N6" si="3">$R6</f>
+        <v>64</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="O6" s="9"/>
+      <c r="P6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R6" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7"/>
       <c r="B7">
-        <v>36.5</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>36.5</v>
+        <v>63</v>
       </c>
       <c r="D7">
-        <v>36.5</v>
+        <v>63</v>
       </c>
       <c r="E7"/>
       <c r="F7" s="2" t="s">
@@ -2815,16 +2844,36 @@
       </c>
       <c r="G7"/>
       <c r="H7" s="8">
-        <v>36.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+      <c r="K7"/>
+      <c r="L7">
+        <f t="shared" ref="L7:N7" si="4">$R7</f>
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R7" s="8">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D8"/>
       <c r="E8" s="9"/>
@@ -2833,19 +2882,36 @@
       </c>
       <c r="G8"/>
       <c r="H8" s="8">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8" t="str">
+        <f t="shared" ref="L8:M8" si="5">$R8&amp;",魔女"</f>
+        <v>62,魔女</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="5"/>
+        <v>62,魔女</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" s="8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9"/>
       <c r="B9">
-        <v>35.5</v>
+        <v>61</v>
       </c>
       <c r="C9">
-        <v>35.5</v>
+        <v>61</v>
       </c>
       <c r="D9">
-        <v>35.5</v>
+        <v>61</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="2" t="s">
@@ -2853,19 +2919,39 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="8">
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9">
+        <f t="shared" ref="L9:N9" si="6">$R9</f>
+        <v>61</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="6"/>
+        <v>61</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="6"/>
+        <v>61</v>
+      </c>
+      <c r="O9"/>
+      <c r="P9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="8">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10"/>
       <c r="B10">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="2" t="s">
@@ -2873,21 +2959,41 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+      <c r="K10"/>
+      <c r="L10">
+        <f>$R10</f>
+        <v>60</v>
+      </c>
+      <c r="M10" t="str">
+        <f>$R10&amp;",魔女"</f>
+        <v>60,魔女</v>
+      </c>
+      <c r="N10">
+        <f>$R10</f>
+        <v>60</v>
+      </c>
+      <c r="O10" s="9"/>
+      <c r="P10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R10" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>34.5</v>
+        <v>59</v>
       </c>
       <c r="B11">
-        <v>34.5</v>
+        <v>59</v>
       </c>
       <c r="C11">
-        <v>34.5</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>34.5</v>
+        <v>59</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="2" t="s">
@@ -2895,19 +3001,42 @@
       </c>
       <c r="G11"/>
       <c r="H11" s="8">
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+      <c r="K11">
+        <f t="shared" ref="K11:N11" si="7">$R11</f>
+        <v>59</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="7"/>
+        <v>59</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="7"/>
+        <v>59</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="7"/>
+        <v>59</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R11" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12"/>
       <c r="B12">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D12">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="2" t="s">
@@ -2915,19 +3044,39 @@
       </c>
       <c r="G12"/>
       <c r="H12" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+      <c r="K12"/>
+      <c r="L12">
+        <f>$R12</f>
+        <v>58</v>
+      </c>
+      <c r="M12" t="str">
+        <f>$R12&amp;",魔女"</f>
+        <v>58,魔女</v>
+      </c>
+      <c r="N12">
+        <f>$R12</f>
+        <v>58</v>
+      </c>
+      <c r="O12" s="9"/>
+      <c r="P12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R12" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13"/>
       <c r="B13">
-        <v>33.5</v>
+        <v>57</v>
       </c>
       <c r="C13">
-        <v>33.5</v>
+        <v>57</v>
       </c>
       <c r="D13">
-        <v>33.5</v>
+        <v>57</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="2" t="s">
@@ -2935,18 +3084,38 @@
       </c>
       <c r="G13"/>
       <c r="H13" s="8">
-        <v>33.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+      <c r="K13"/>
+      <c r="L13">
+        <f t="shared" ref="L13:N13" si="8">$R13</f>
+        <v>57</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="8"/>
+        <v>57</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="8"/>
+        <v>57</v>
+      </c>
+      <c r="O13"/>
+      <c r="P13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R13" s="8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B14">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C14">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D14"/>
       <c r="E14" s="9"/>
@@ -2955,19 +3124,39 @@
       </c>
       <c r="G14"/>
       <c r="H14" s="8">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+      <c r="K14">
+        <f t="shared" ref="K14:M14" si="9">$R14</f>
+        <v>56</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="9"/>
+        <v>56</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="9"/>
+        <v>56</v>
+      </c>
+      <c r="N14"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R14" s="8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="2" t="s">
@@ -2975,19 +3164,39 @@
       </c>
       <c r="G15"/>
       <c r="H15" s="8">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15" t="str">
+        <f t="shared" ref="L15:N15" si="10">$R15&amp;",魔女"</f>
+        <v>55,魔女</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="10"/>
+        <v>55,魔女</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="10"/>
+        <v>55,魔女</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R15" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16"/>
       <c r="B16">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C16">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D16">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="2" t="s">
@@ -2995,19 +3204,39 @@
       </c>
       <c r="G16"/>
       <c r="H16" s="8">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+      <c r="K16"/>
+      <c r="L16">
+        <f t="shared" ref="L16:N16" si="11">$R16</f>
+        <v>54</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="11"/>
+        <v>54</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="11"/>
+        <v>54</v>
+      </c>
+      <c r="O16" s="9"/>
+      <c r="P16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R16" s="8">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17"/>
       <c r="B17">
-        <v>31.5</v>
+        <v>53</v>
       </c>
       <c r="C17">
-        <v>31.5</v>
+        <v>53</v>
       </c>
       <c r="D17">
-        <v>31.5</v>
+        <v>53</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="2" t="s">
@@ -3015,18 +3244,38 @@
       </c>
       <c r="G17"/>
       <c r="H17" s="8">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17">
+        <f t="shared" ref="L17:N17" si="12">$R17</f>
+        <v>53</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="12"/>
+        <v>53</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="12"/>
+        <v>53</v>
+      </c>
+      <c r="O17"/>
+      <c r="P17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R17" s="8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="B18">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C18">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D18"/>
       <c r="E18" s="9"/>
@@ -3035,19 +3284,39 @@
       </c>
       <c r="G18"/>
       <c r="H18" s="8">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+      <c r="K18">
+        <f t="shared" ref="K18:M18" si="13">$R18</f>
+        <v>52</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="13"/>
+        <v>52</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="13"/>
+        <v>52</v>
+      </c>
+      <c r="N18"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R18" s="8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19"/>
       <c r="B19">
-        <v>30.5</v>
+        <v>51</v>
       </c>
       <c r="C19">
-        <v>30.5</v>
+        <v>51</v>
       </c>
       <c r="D19">
-        <v>30.5</v>
+        <v>51</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="2" t="s">
@@ -3055,19 +3324,39 @@
       </c>
       <c r="G19"/>
       <c r="H19" s="8">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19">
+        <f t="shared" ref="L19:N19" si="14">$R19</f>
+        <v>51</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="14"/>
+        <v>51</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="14"/>
+        <v>51</v>
+      </c>
+      <c r="O19"/>
+      <c r="P19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" s="8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="2" t="s">
@@ -3075,19 +3364,39 @@
       </c>
       <c r="G20"/>
       <c r="H20" s="8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+      <c r="K20"/>
+      <c r="L20" t="str">
+        <f t="shared" ref="L20:N20" si="15">$R20&amp;",魔女"</f>
+        <v>50,魔女</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="15"/>
+        <v>50,魔女</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="15"/>
+        <v>50,魔女</v>
+      </c>
+      <c r="O20" s="9"/>
+      <c r="P20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21"/>
       <c r="B21">
-        <v>29.5</v>
+        <v>49</v>
       </c>
       <c r="C21">
-        <v>29.5</v>
+        <v>49</v>
       </c>
       <c r="D21">
-        <v>29.5</v>
+        <v>49</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="2" t="s">
@@ -3095,18 +3404,38 @@
       </c>
       <c r="G21"/>
       <c r="H21" s="8">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+      <c r="K21"/>
+      <c r="L21">
+        <f t="shared" ref="L21:N21" si="16">$R21</f>
+        <v>49</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="16"/>
+        <v>49</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="16"/>
+        <v>49</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R21" s="8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B22">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C22">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D22"/>
       <c r="E22" s="9"/>
@@ -3115,19 +3444,39 @@
       </c>
       <c r="G22"/>
       <c r="H22" s="8">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+      <c r="K22">
+        <f t="shared" ref="K22:M22" si="17">$R22</f>
+        <v>48</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="17"/>
+        <v>48</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="17"/>
+        <v>48</v>
+      </c>
+      <c r="N22"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23"/>
       <c r="B23">
-        <v>28.5</v>
+        <v>47</v>
       </c>
       <c r="C23">
-        <v>28.5</v>
+        <v>47</v>
       </c>
       <c r="D23">
-        <v>28.5</v>
+        <v>47</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="2" t="s">
@@ -3135,16 +3484,36 @@
       </c>
       <c r="G23"/>
       <c r="H23" s="8">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+      <c r="K23"/>
+      <c r="L23">
+        <f t="shared" ref="L23:N23" si="18">$R23</f>
+        <v>47</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="18"/>
+        <v>47</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="18"/>
+        <v>47</v>
+      </c>
+      <c r="O23"/>
+      <c r="P23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R23" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24"/>
       <c r="B24">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C24">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D24"/>
       <c r="E24" s="9"/>
@@ -3153,18 +3522,35 @@
       </c>
       <c r="G24"/>
       <c r="H24" s="8">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+      <c r="K24"/>
+      <c r="L24">
+        <f t="shared" ref="L24:M24" si="19">$R24</f>
+        <v>46</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="19"/>
+        <v>46</v>
+      </c>
+      <c r="N24"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R24" s="8">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>27.5</v>
+        <v>45</v>
       </c>
       <c r="B25">
-        <v>27.5</v>
+        <v>45</v>
       </c>
       <c r="C25">
-        <v>27.5</v>
+        <v>45</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -3173,19 +3559,39 @@
       </c>
       <c r="G25"/>
       <c r="H25" s="8">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+      <c r="K25">
+        <f t="shared" ref="K25:L26" si="20">$R25</f>
+        <v>45</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="20"/>
+        <v>45</v>
+      </c>
+      <c r="M25">
+        <f>$R25</f>
+        <v>45</v>
+      </c>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" s="8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B26">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C26"/>
       <c r="D26">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="2" t="s">
@@ -3193,41 +3599,84 @@
       </c>
       <c r="G26"/>
       <c r="H26" s="8">
+        <v>44</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="20"/>
+        <v>44</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="20"/>
+        <v>44</v>
+      </c>
+      <c r="M26"/>
+      <c r="N26">
+        <f>$R26</f>
+        <v>44</v>
+      </c>
+      <c r="O26" s="9"/>
+      <c r="P26" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="R26" s="8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="E27" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G27"/>
       <c r="H27" s="8">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+      <c r="K27" t="str">
+        <f t="shared" ref="K27:L27" si="21">$R27&amp;",魔女"</f>
+        <v>43,魔女</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="21"/>
+        <v>43,魔女</v>
+      </c>
+      <c r="M27"/>
+      <c r="N27" t="str">
+        <f t="shared" ref="N27:O27" si="22">$R27&amp;",魔女"</f>
+        <v>43,魔女</v>
+      </c>
+      <c r="O27" t="str">
+        <f t="shared" si="22"/>
+        <v>43,魔女</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R27" s="8">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C28"/>
       <c r="D28">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="2" t="s">
@@ -3235,41 +3684,84 @@
       </c>
       <c r="G28"/>
       <c r="H28" s="8">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+      <c r="K28">
+        <f t="shared" ref="K28:L32" si="23">$R28</f>
+        <v>42</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="23"/>
+        <v>42</v>
+      </c>
+      <c r="M28"/>
+      <c r="N28">
+        <f t="shared" ref="N28:N32" si="24">$R28</f>
+        <v>42</v>
+      </c>
+      <c r="O28" s="9"/>
+      <c r="P28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R28" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>25.5</v>
+        <v>41</v>
       </c>
       <c r="B29">
-        <v>25.5</v>
+        <v>41</v>
       </c>
       <c r="C29"/>
       <c r="D29">
-        <v>25.5</v>
+        <v>41</v>
       </c>
       <c r="E29">
-        <v>25.5</v>
+        <v>41</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G29"/>
       <c r="H29" s="8">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="23"/>
+        <v>41</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="23"/>
+        <v>41</v>
+      </c>
+      <c r="M29"/>
+      <c r="N29">
+        <f t="shared" si="24"/>
+        <v>41</v>
+      </c>
+      <c r="O29">
+        <f>$R29</f>
+        <v>41</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R29" s="8">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B30">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C30"/>
       <c r="D30">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="2" t="s">
@@ -3277,41 +3769,84 @@
       </c>
       <c r="G30"/>
       <c r="H30" s="8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>40</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="23"/>
+        <v>40</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="23"/>
+        <v>40</v>
+      </c>
+      <c r="M30"/>
+      <c r="N30">
+        <f t="shared" si="24"/>
+        <v>40</v>
+      </c>
+      <c r="O30" s="9"/>
+      <c r="P30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R30" s="8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>24.5</v>
+        <v>39</v>
       </c>
       <c r="B31">
-        <v>24.5</v>
+        <v>39</v>
       </c>
       <c r="C31"/>
       <c r="D31">
-        <v>24.5</v>
+        <v>39</v>
       </c>
       <c r="E31">
-        <v>24.5</v>
+        <v>39</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G31"/>
       <c r="H31" s="8">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="23"/>
+        <v>39</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="23"/>
+        <v>39</v>
+      </c>
+      <c r="M31"/>
+      <c r="N31">
+        <f t="shared" si="24"/>
+        <v>39</v>
+      </c>
+      <c r="O31">
+        <f>$R31</f>
+        <v>39</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B32">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C32"/>
       <c r="D32">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="2" t="s">
@@ -3319,43 +3854,86 @@
       </c>
       <c r="G32"/>
       <c r="H32" s="8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>38</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="23"/>
+        <v>38</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="23"/>
+        <v>38</v>
+      </c>
+      <c r="M32"/>
+      <c r="N32">
+        <f t="shared" si="24"/>
+        <v>38</v>
+      </c>
+      <c r="O32" s="9"/>
+      <c r="P32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R32" s="8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E33" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G33"/>
       <c r="H33" s="8">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>37</v>
+      </c>
+      <c r="K33" t="str">
+        <f t="shared" ref="K33:L33" si="25">$R33&amp;",魔女"</f>
+        <v>37,魔女</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="25"/>
+        <v>37,魔女</v>
+      </c>
+      <c r="M33"/>
+      <c r="N33" t="str">
+        <f t="shared" ref="N33:O33" si="26">$R33&amp;",魔女"</f>
+        <v>37,魔女</v>
+      </c>
+      <c r="O33" t="str">
+        <f t="shared" si="26"/>
+        <v>37,魔女</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R33" s="8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B34">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C34">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D34">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="2" t="s">
@@ -3363,19 +3941,42 @@
       </c>
       <c r="G34"/>
       <c r="H34" s="8">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+      <c r="K34">
+        <f t="shared" ref="K34:N34" si="27">$R34</f>
+        <v>36</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="27"/>
+        <v>36</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="27"/>
+        <v>36</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="27"/>
+        <v>36</v>
+      </c>
+      <c r="O34" s="9"/>
+      <c r="P34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" s="8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35"/>
       <c r="B35">
-        <v>22.5</v>
+        <v>35</v>
       </c>
       <c r="C35">
-        <v>22.5</v>
+        <v>35</v>
       </c>
       <c r="D35">
-        <v>22.5</v>
+        <v>35</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="2" t="s">
@@ -3383,16 +3984,36 @@
       </c>
       <c r="G35"/>
       <c r="H35" s="8">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+      <c r="K35"/>
+      <c r="L35">
+        <f t="shared" ref="L35:N35" si="28">$R35</f>
+        <v>35</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="28"/>
+        <v>35</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="28"/>
+        <v>35</v>
+      </c>
+      <c r="O35"/>
+      <c r="P35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R35" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36"/>
       <c r="B36">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C36">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D36"/>
       <c r="E36" s="9"/>
@@ -3401,19 +4022,36 @@
       </c>
       <c r="G36"/>
       <c r="H36" s="8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+      <c r="K36"/>
+      <c r="L36">
+        <f t="shared" ref="L36:M36" si="29">$R36</f>
+        <v>34</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="29"/>
+        <v>34</v>
+      </c>
+      <c r="N36"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R36" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37"/>
       <c r="B37">
-        <v>21.5</v>
+        <v>33</v>
       </c>
       <c r="C37">
-        <v>21.5</v>
+        <v>33</v>
       </c>
       <c r="D37">
-        <v>21.5</v>
+        <v>33</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="2" t="s">
@@ -3421,16 +4059,36 @@
       </c>
       <c r="G37"/>
       <c r="H37" s="8">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+      <c r="K37"/>
+      <c r="L37">
+        <f t="shared" ref="L37:N37" si="30">$R37</f>
+        <v>33</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="30"/>
+        <v>33</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="30"/>
+        <v>33</v>
+      </c>
+      <c r="O37"/>
+      <c r="P37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R37" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="D38"/>
       <c r="E38" s="9"/>
@@ -3439,19 +4097,36 @@
       </c>
       <c r="G38"/>
       <c r="H38" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+      <c r="K38"/>
+      <c r="L38" t="str">
+        <f t="shared" ref="L38:M38" si="31">$R38&amp;",魔女"</f>
+        <v>32,魔女</v>
+      </c>
+      <c r="M38" t="str">
+        <f t="shared" si="31"/>
+        <v>32,魔女</v>
+      </c>
+      <c r="N38"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R38" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39"/>
       <c r="B39">
-        <v>20.5</v>
+        <v>31</v>
       </c>
       <c r="C39">
-        <v>20.5</v>
+        <v>31</v>
       </c>
       <c r="D39">
-        <v>20.5</v>
+        <v>31</v>
       </c>
       <c r="E39"/>
       <c r="F39" s="2" t="s">
@@ -3459,16 +4134,36 @@
       </c>
       <c r="G39"/>
       <c r="H39" s="8">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="K39"/>
+      <c r="L39">
+        <f t="shared" ref="L39:N39" si="32">$R39</f>
+        <v>31</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="32"/>
+        <v>31</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="32"/>
+        <v>31</v>
+      </c>
+      <c r="O39"/>
+      <c r="P39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R39" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40"/>
       <c r="B40">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D40"/>
       <c r="E40" s="9"/>
@@ -3477,19 +4172,36 @@
       </c>
       <c r="G40"/>
       <c r="H40" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+      <c r="K40"/>
+      <c r="L40">
+        <f t="shared" ref="L40:M40" si="33">$R40</f>
+        <v>30</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="33"/>
+        <v>30</v>
+      </c>
+      <c r="N40"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R40" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41"/>
       <c r="B41">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="C41">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="D41">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="E41"/>
       <c r="F41" s="2" t="s">
@@ -3497,21 +4209,41 @@
       </c>
       <c r="G41"/>
       <c r="H41" s="8">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+      <c r="K41"/>
+      <c r="L41">
+        <f t="shared" ref="L41:N41" si="34">$R41</f>
+        <v>29</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="34"/>
+        <v>29</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="34"/>
+        <v>29</v>
+      </c>
+      <c r="O41"/>
+      <c r="P41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R41" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B42">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C42">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D42">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="2" t="s">
@@ -3519,41 +4251,86 @@
       </c>
       <c r="G42"/>
       <c r="H42" s="8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+      <c r="K42">
+        <f t="shared" ref="K42:N42" si="35">$R42</f>
+        <v>28</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="35"/>
+        <v>28</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="35"/>
+        <v>28</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="35"/>
+        <v>28</v>
+      </c>
+      <c r="O42" s="9"/>
+      <c r="P42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R42" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B43"/>
       <c r="C43">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="D43">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="E43">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G43"/>
       <c r="H43" s="8">
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+      <c r="K43">
+        <v>30</v>
+      </c>
+      <c r="L43"/>
+      <c r="M43">
+        <f t="shared" ref="M43:O43" si="36">$R43</f>
+        <v>27</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="36"/>
+        <v>27</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="36"/>
+        <v>27</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R43" s="8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B44"/>
       <c r="C44" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="D44" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="2" t="s">
@@ -3561,34 +4338,75 @@
       </c>
       <c r="G44"/>
       <c r="H44" s="8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+      <c r="K44">
+        <v>32</v>
+      </c>
+      <c r="L44"/>
+      <c r="M44" t="str">
+        <f t="shared" ref="M44:N44" si="37">$R44&amp;",魔女"</f>
+        <v>26,魔女</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="37"/>
+        <v>26,魔女</v>
+      </c>
+      <c r="O44" s="9"/>
+      <c r="P44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R44" s="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B45"/>
       <c r="C45">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="E45">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G45"/>
       <c r="H45" s="8">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+      <c r="K45">
+        <v>34</v>
+      </c>
+      <c r="L45"/>
+      <c r="M45">
+        <f t="shared" ref="M45:O45" si="38">$R45</f>
+        <v>25</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="38"/>
+        <v>25</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="38"/>
+        <v>25</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R45" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B46"/>
       <c r="C46">
@@ -3603,41 +4421,80 @@
       </c>
       <c r="G46"/>
       <c r="H46" s="8">
+        <v>24</v>
+      </c>
+      <c r="K46">
+        <v>36</v>
+      </c>
+      <c r="L46"/>
+      <c r="M46">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="N46">
+        <v>17</v>
+      </c>
+      <c r="O46" s="9"/>
+      <c r="P46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R46" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B47"/>
       <c r="C47">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="E47">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>48</v>
       </c>
       <c r="G47"/>
       <c r="H47" s="8">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>23</v>
+      </c>
+      <c r="K47">
+        <v>38</v>
+      </c>
+      <c r="L47"/>
+      <c r="M47">
+        <f>$R47</f>
+        <v>23</v>
+      </c>
+      <c r="N47" t="str">
+        <f>$R47&amp;",魔女"</f>
+        <v>23,魔女</v>
+      </c>
+      <c r="O47">
+        <f>$R47</f>
+        <v>23</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R47" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>40</v>
       </c>
       <c r="B48"/>
       <c r="C48">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D48">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E48" s="9"/>
       <c r="F48" s="2" t="s">
@@ -3645,19 +4502,38 @@
       </c>
       <c r="G48"/>
       <c r="H48" s="8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>22</v>
+      </c>
+      <c r="K48">
+        <v>40</v>
+      </c>
+      <c r="L48"/>
+      <c r="M48">
+        <f t="shared" ref="M48:N48" si="39">$R48</f>
+        <v>22</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="39"/>
+        <v>22</v>
+      </c>
+      <c r="O48" s="9"/>
+      <c r="P48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R48" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49"/>
       <c r="C49">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="D49">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="E49"/>
       <c r="F49" s="2" t="s">
@@ -3665,16 +4541,35 @@
       </c>
       <c r="G49"/>
       <c r="H49" s="8">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+      <c r="K49">
+        <v>50</v>
+      </c>
+      <c r="L49"/>
+      <c r="M49">
+        <f t="shared" ref="M49:N49" si="40">$R49</f>
+        <v>21</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="40"/>
+        <v>21</v>
+      </c>
+      <c r="O49"/>
+      <c r="P49" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R49" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="D50"/>
       <c r="E50" s="9"/>
@@ -3683,19 +4578,36 @@
       </c>
       <c r="G50"/>
       <c r="H50" s="8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+      <c r="K50"/>
+      <c r="L50" t="str">
+        <f t="shared" ref="L50:M50" si="41">$R50&amp;",魔女"</f>
+        <v>20,魔女</v>
+      </c>
+      <c r="M50" t="str">
+        <f t="shared" si="41"/>
+        <v>20,魔女</v>
+      </c>
+      <c r="N50"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R50" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51"/>
       <c r="B51">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="C51">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="D51">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="E51"/>
       <c r="F51" s="2" t="s">
@@ -3703,16 +4615,36 @@
       </c>
       <c r="G51"/>
       <c r="H51" s="8">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+      <c r="K51"/>
+      <c r="L51">
+        <f t="shared" ref="L51:N51" si="42">$R51</f>
+        <v>19</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="42"/>
+        <v>19</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="42"/>
+        <v>19</v>
+      </c>
+      <c r="O51"/>
+      <c r="P51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R51" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52"/>
       <c r="B52">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C52">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D52"/>
       <c r="E52" s="9"/>
@@ -3721,19 +4653,36 @@
       </c>
       <c r="G52"/>
       <c r="H52" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+      <c r="K52"/>
+      <c r="L52">
+        <f>$R52</f>
+        <v>18</v>
+      </c>
+      <c r="M52">
+        <f>$R52</f>
+        <v>18</v>
+      </c>
+      <c r="N52"/>
+      <c r="O52" s="9"/>
+      <c r="P52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R52" s="8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53"/>
       <c r="B53">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D53">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="E53"/>
       <c r="F53" s="2" t="s">
@@ -3741,16 +4690,36 @@
       </c>
       <c r="G53"/>
       <c r="H53" s="8">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+      <c r="K53"/>
+      <c r="L53">
+        <f>$R53</f>
+        <v>17</v>
+      </c>
+      <c r="M53" t="str">
+        <f>$R53&amp;",魔女"</f>
+        <v>17,魔女</v>
+      </c>
+      <c r="N53">
+        <f>$R53</f>
+        <v>17</v>
+      </c>
+      <c r="O53"/>
+      <c r="P53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R53" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54"/>
       <c r="B54">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C54">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D54"/>
       <c r="E54" s="9"/>
@@ -3759,19 +4728,36 @@
       </c>
       <c r="G54"/>
       <c r="H54" s="8">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+      <c r="K54"/>
+      <c r="L54">
+        <f>$R54</f>
+        <v>16</v>
+      </c>
+      <c r="M54">
+        <f>$R54</f>
+        <v>16</v>
+      </c>
+      <c r="N54"/>
+      <c r="O54" s="9"/>
+      <c r="P54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R54" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55"/>
       <c r="B55">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="C55">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="D55">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="E55"/>
       <c r="F55" s="2" t="s">
@@ -3779,16 +4765,36 @@
       </c>
       <c r="G55"/>
       <c r="H55" s="8">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+      <c r="K55"/>
+      <c r="L55">
+        <f>$R55</f>
+        <v>15</v>
+      </c>
+      <c r="M55">
+        <f>$R55</f>
+        <v>15</v>
+      </c>
+      <c r="N55">
+        <f>$R55</f>
+        <v>15</v>
+      </c>
+      <c r="O55"/>
+      <c r="P55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R55" s="8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="D56"/>
       <c r="E56" s="9"/>
@@ -3797,19 +4803,36 @@
       </c>
       <c r="G56"/>
       <c r="H56" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+      <c r="K56"/>
+      <c r="L56" t="str">
+        <f t="shared" ref="L56:M56" si="43">$R56&amp;",魔女"</f>
+        <v>14,魔女</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="43"/>
+        <v>14,魔女</v>
+      </c>
+      <c r="N56"/>
+      <c r="O56" s="9"/>
+      <c r="P56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R56" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57"/>
-      <c r="B57">
-        <v>11.5</v>
-      </c>
-      <c r="C57">
-        <v>11.5</v>
-      </c>
-      <c r="D57">
-        <v>11.5</v>
+      <c r="B57" s="8">
+        <v>13</v>
+      </c>
+      <c r="C57" s="8">
+        <v>13</v>
+      </c>
+      <c r="D57" s="8">
+        <v>13</v>
       </c>
       <c r="E57"/>
       <c r="F57" s="2" t="s">
@@ -3817,16 +4840,36 @@
       </c>
       <c r="G57"/>
       <c r="H57" s="8">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+      <c r="K57"/>
+      <c r="L57">
+        <f>$R57</f>
+        <v>13</v>
+      </c>
+      <c r="M57">
+        <f>$R57</f>
+        <v>13</v>
+      </c>
+      <c r="N57">
+        <f>$R57</f>
+        <v>13</v>
+      </c>
+      <c r="O57"/>
+      <c r="P57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="R57" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58"/>
-      <c r="B58">
-        <v>11</v>
-      </c>
-      <c r="C58">
-        <v>11</v>
+      <c r="B58" s="8">
+        <v>12</v>
+      </c>
+      <c r="C58" s="8">
+        <v>12</v>
       </c>
       <c r="D58"/>
       <c r="E58" s="9"/>
@@ -3835,30 +4878,67 @@
       </c>
       <c r="G58"/>
       <c r="H58" s="8">
+        <v>12</v>
+      </c>
+      <c r="K58"/>
+      <c r="L58">
+        <f>$R58</f>
+        <v>12</v>
+      </c>
+      <c r="M58">
+        <f>$R58</f>
+        <v>12</v>
+      </c>
+      <c r="N58"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="R58" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59"/>
+      <c r="B59" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59"/>
-      <c r="B59">
-        <v>10.5</v>
-      </c>
       <c r="C59" t="s">
-        <v>150</v>
-      </c>
-      <c r="D59">
-        <v>10.5</v>
+        <v>172</v>
+      </c>
+      <c r="D59" s="8">
+        <v>11</v>
       </c>
       <c r="E59"/>
       <c r="F59" s="2" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="G59"/>
       <c r="H59" s="8">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+      <c r="K59"/>
+      <c r="L59">
+        <f>$R59</f>
+        <v>11</v>
+      </c>
+      <c r="M59" t="str">
+        <f>$R59&amp;",魔女"</f>
+        <v>11,魔女</v>
+      </c>
+      <c r="N59">
+        <f>$R59</f>
+        <v>11</v>
+      </c>
+      <c r="O59"/>
+      <c r="P59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R59" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60"/>
       <c r="B60">
         <v>10</v>
@@ -3869,14 +4949,31 @@
       <c r="D60"/>
       <c r="E60" s="9"/>
       <c r="F60" s="2" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="G60"/>
       <c r="H60" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K60"/>
+      <c r="L60">
+        <f>$R60</f>
+        <v>10</v>
+      </c>
+      <c r="M60">
+        <f>$R60</f>
+        <v>10</v>
+      </c>
+      <c r="N60"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R60" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="8">
         <v>0</v>
       </c>
@@ -3890,6 +4987,21 @@
         <v>3</v>
       </c>
       <c r="E61" s="8">
+        <v>4</v>
+      </c>
+      <c r="K61" s="8">
+        <v>0</v>
+      </c>
+      <c r="L61" s="8">
+        <v>1</v>
+      </c>
+      <c r="M61" s="8">
+        <v>2</v>
+      </c>
+      <c r="N61" s="8">
+        <v>3</v>
+      </c>
+      <c r="O61" s="8">
         <v>4</v>
       </c>
     </row>
@@ -3906,52 +5018,52 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="L1" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="M1" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="N1" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="O1" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="P1" s="18" t="s">
         <v>96</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.4">
@@ -3962,7 +5074,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D2" s="18">
         <v>9</v>
@@ -3998,7 +5110,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P2" s="18">
         <v>0</v>
@@ -4018,7 +5130,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3" s="18">
         <v>4</v>
@@ -4054,7 +5166,7 @@
         <v>0.75</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P3" s="18">
         <v>1</v>
@@ -4079,7 +5191,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" s="18">
         <v>8</v>
@@ -4115,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P4" s="18">
         <v>2</v>
@@ -4140,7 +5252,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D5" s="18">
         <v>3</v>
@@ -4176,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P5" s="18">
         <v>3</v>
@@ -4201,7 +5313,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D6" s="18">
         <v>8</v>
@@ -4237,7 +5349,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P6" s="18">
         <v>2</v>
@@ -4262,7 +5374,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D7" s="18">
         <v>6</v>
@@ -4298,7 +5410,7 @@
         <v>0.75</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P7" s="18">
         <v>3</v>
@@ -4323,7 +5435,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D8" s="18">
         <v>6</v>
@@ -4359,7 +5471,7 @@
         <v>0.75</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P8" s="18">
         <v>0</v>
@@ -4384,7 +5496,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D9" s="18">
         <v>3</v>
@@ -4420,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P9" s="18">
         <v>2</v>
@@ -4445,7 +5557,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D10" s="18">
         <v>1</v>
@@ -4481,7 +5593,7 @@
         <v>1.25</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P10" s="18">
         <v>1</v>
@@ -4513,7 +5625,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R12">
         <v>10</v>
@@ -4542,7 +5654,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R14">
         <v>12</v>
@@ -4558,7 +5670,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R15">
         <v>13</v>
@@ -4574,7 +5686,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R16">
         <v>14</v>
@@ -4603,7 +5715,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="R18">
         <v>16</v>
@@ -4632,7 +5744,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="R20">
         <v>18</v>
@@ -4648,7 +5760,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R21">
         <v>19</v>
@@ -4677,7 +5789,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="R23">
         <v>21</v>
@@ -4693,7 +5805,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R24">
         <v>22</v>
@@ -4709,7 +5821,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R25">
         <v>23</v>
@@ -4725,7 +5837,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R26">
         <v>24</v>
@@ -4754,7 +5866,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R28">
         <v>26</v>
@@ -4783,7 +5895,7 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R30">
         <v>28</v>
@@ -4799,35 +5911,35 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A31" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
       <c r="H31" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="K31" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="J31" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="K31" s="18" t="s">
-        <v>96</v>
-      </c>
       <c r="L31" s="18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R31">
         <v>29</v>
@@ -4847,7 +5959,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D32" s="18">
         <v>100000</v>
@@ -4891,7 +6003,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D33" s="18">
         <v>110000</v>
@@ -4935,7 +6047,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D34" s="18">
         <v>120000</v>
@@ -4979,7 +6091,7 @@
         <v>13</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D35" s="18">
         <v>130000</v>
@@ -5023,7 +6135,7 @@
         <v>20</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D36" s="18">
         <v>200000</v>
@@ -5067,7 +6179,7 @@
         <v>30</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D37" s="18">
         <v>300000</v>
@@ -5111,7 +6223,7 @@
         <v>40</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D38" s="18">
         <v>400000</v>
@@ -5155,7 +6267,7 @@
         <v>50</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D39" s="18">
         <v>500000</v>
@@ -5208,7 +6320,7 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R41">
         <v>39</v>
@@ -5224,7 +6336,7 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R42">
         <v>40</v>
@@ -5240,15 +6352,15 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A44" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.4">
@@ -5256,7 +6368,7 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="R45">
         <v>43</v>
@@ -5275,7 +6387,7 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R46">
         <v>44</v>
@@ -5294,7 +6406,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R47">
         <v>45</v>
@@ -5313,7 +6425,7 @@
         <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R48">
         <v>46</v>
@@ -5521,31 +6633,31 @@
   <sheetFormatPr defaultColWidth="4.5" defaultRowHeight="36" customHeight="1" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21">
+      <c r="A1" s="22">
         <f>MAP!A1</f>
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22">
         <f>MAP!B1</f>
         <v>0</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21" t="str">
+      <c r="D1" s="22"/>
+      <c r="E1" s="22" t="str">
         <f>MAP!C1</f>
         <v>top of tower</v>
       </c>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21">
+      <c r="F1" s="22"/>
+      <c r="G1" s="22">
         <f>MAP!D1</f>
         <v>0</v>
       </c>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21">
+      <c r="H1" s="22"/>
+      <c r="I1" s="22">
         <f>MAP!E1</f>
         <v>0</v>
       </c>
-      <c r="J1" s="21"/>
+      <c r="J1" s="22"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
@@ -5555,53 +6667,53 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="21">
+      <c r="B2" s="22">
         <f>MAP!A2</f>
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21" t="str">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22" t="str">
         <f>MAP!B2</f>
         <v>白</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21" t="str">
+      <c r="E2" s="22"/>
+      <c r="F2" s="22" t="str">
         <f>MAP!C2</f>
         <v>白</v>
       </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21">
+      <c r="G2" s="22"/>
+      <c r="H2" s="22">
         <f>MAP!D2</f>
         <v>0</v>
       </c>
-      <c r="I2" s="21"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21">
+      <c r="A3" s="22">
         <f>MAP!A3</f>
         <v>0</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21" t="str">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22" t="str">
         <f>MAP!B3</f>
         <v>黄</v>
       </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21" t="str">
+      <c r="D3" s="22"/>
+      <c r="E3" s="22" t="str">
         <f>MAP!C3</f>
         <v>青</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21" t="str">
+      <c r="F3" s="22"/>
+      <c r="G3" s="22" t="str">
         <f>MAP!D3</f>
         <v>赤</v>
       </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21">
+      <c r="H3" s="22"/>
+      <c r="I3" s="22">
         <f>MAP!E3</f>
         <v>0</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="22"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -5609,26 +6721,26 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="21" t="str">
+      <c r="B4" s="22" t="str">
         <f>MAP!A4</f>
         <v>青</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21" t="str">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22" t="str">
         <f>MAP!B4</f>
         <v>黄</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21" t="str">
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="str">
         <f>MAP!C4</f>
         <v>緑</v>
       </c>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21">
+      <c r="G4" s="22"/>
+      <c r="H4" s="22">
         <f>MAP!D4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="21"/>
+      <c r="I4" s="22"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -5637,57 +6749,57 @@
       <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="21">
+      <c r="A5" s="22">
         <f>MAP!A5</f>
         <v>0</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21" t="str">
+      <c r="B5" s="22"/>
+      <c r="C5" s="22" t="str">
         <f>MAP!B5</f>
         <v>紫</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="str">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="str">
         <f>MAP!C5</f>
         <v>緑</v>
       </c>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="str">
+      <c r="F5" s="22"/>
+      <c r="G5" s="22" t="str">
         <f>MAP!D5</f>
         <v>黄</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21">
+      <c r="H5" s="22"/>
+      <c r="I5" s="22">
         <f>MAP!E5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="22"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="21" t="str">
+      <c r="B6" s="22" t="str">
         <f>MAP!A6</f>
         <v>黄</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21" t="str">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22" t="str">
         <f>MAP!B6</f>
         <v>赤</v>
       </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21" t="str">
+      <c r="E6" s="22"/>
+      <c r="F6" s="22" t="str">
         <f>MAP!C6</f>
         <v>紫</v>
       </c>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21" t="str">
+      <c r="G6" s="22"/>
+      <c r="H6" s="22" t="str">
         <f>MAP!D6</f>
         <v>緑</v>
       </c>
-      <c r="I6" s="21"/>
+      <c r="I6" s="22"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -5695,57 +6807,57 @@
       <c r="N6" s="6"/>
     </row>
     <row r="7" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="21">
+      <c r="A7" s="22">
         <f>MAP!A7</f>
         <v>0</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21" t="str">
+      <c r="B7" s="22"/>
+      <c r="C7" s="22" t="str">
         <f>MAP!B7</f>
         <v>青</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21" t="str">
+      <c r="D7" s="22"/>
+      <c r="E7" s="22" t="str">
         <f>MAP!C7</f>
         <v>紫</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21" t="str">
+      <c r="F7" s="22"/>
+      <c r="G7" s="22" t="str">
         <f>MAP!D7</f>
         <v>赤</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21">
+      <c r="H7" s="22"/>
+      <c r="I7" s="22">
         <f>MAP!E7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="21"/>
+      <c r="J7" s="22"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="21">
+      <c r="B8" s="22">
         <f>MAP!A8</f>
         <v>0</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21" t="str">
+      <c r="C8" s="22"/>
+      <c r="D8" s="22" t="str">
         <f>MAP!B8</f>
         <v>黒</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21" t="str">
+      <c r="E8" s="22"/>
+      <c r="F8" s="22" t="str">
         <f>MAP!C8</f>
         <v>黒</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21">
+      <c r="G8" s="22"/>
+      <c r="H8" s="22">
         <f>MAP!D8</f>
         <v>0</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -5753,57 +6865,57 @@
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="21">
+      <c r="A9" s="22">
         <f>MAP!A9</f>
         <v>0</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21" t="str">
+      <c r="B9" s="22"/>
+      <c r="C9" s="22" t="str">
         <f>MAP!B9</f>
         <v>黒</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21" t="str">
+      <c r="D9" s="22"/>
+      <c r="E9" s="22" t="str">
         <f>MAP!C9</f>
         <v>黒</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21" t="str">
+      <c r="F9" s="22"/>
+      <c r="G9" s="22" t="str">
         <f>MAP!D9</f>
         <v>外</v>
       </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21">
+      <c r="H9" s="22"/>
+      <c r="I9" s="22">
         <f>MAP!E9</f>
         <v>0</v>
       </c>
-      <c r="J9" s="21"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="21">
+      <c r="B10" s="22">
         <f>MAP!A10</f>
         <v>0</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21" t="str">
+      <c r="C10" s="22"/>
+      <c r="D10" s="22" t="str">
         <f>MAP!B10</f>
         <v>黒</v>
       </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21" t="str">
+      <c r="E10" s="22"/>
+      <c r="F10" s="22" t="str">
         <f>MAP!C10</f>
         <v>黒</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21" t="str">
+      <c r="G10" s="22"/>
+      <c r="H10" s="22" t="str">
         <f>MAP!D10</f>
         <v>黒</v>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="22"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
@@ -5811,57 +6923,57 @@
       <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="22" t="str">
         <f>MAP!A11</f>
         <v>外</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21" t="str">
+      <c r="B11" s="22"/>
+      <c r="C11" s="22" t="str">
         <f>MAP!B11</f>
         <v>黒</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21" t="str">
+      <c r="D11" s="22"/>
+      <c r="E11" s="22" t="str">
         <f>MAP!C11</f>
         <v>黒</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21" t="str">
+      <c r="F11" s="22"/>
+      <c r="G11" s="22" t="str">
         <f>MAP!D11</f>
         <v>黒</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21">
+      <c r="H11" s="22"/>
+      <c r="I11" s="22">
         <f>MAP!E11</f>
         <v>0</v>
       </c>
-      <c r="J11" s="21"/>
+      <c r="J11" s="22"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="21">
+      <c r="B12" s="22">
         <f>MAP!A12</f>
         <v>0</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21" t="str">
+      <c r="C12" s="22"/>
+      <c r="D12" s="22" t="str">
         <f>MAP!B12</f>
         <v>黒</v>
       </c>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21" t="str">
+      <c r="E12" s="22"/>
+      <c r="F12" s="22" t="str">
         <f>MAP!C12</f>
         <v>黒</v>
       </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21" t="str">
+      <c r="G12" s="22"/>
+      <c r="H12" s="22" t="str">
         <f>MAP!D12</f>
         <v>外</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="22"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
@@ -5869,1207 +6981,1459 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="21">
+      <c r="A13" s="22">
         <f>MAP!A13</f>
         <v>0</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21" t="str">
+      <c r="B13" s="22"/>
+      <c r="C13" s="22" t="str">
         <f>MAP!B13</f>
         <v>黒</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21" t="str">
+      <c r="D13" s="22"/>
+      <c r="E13" s="22" t="str">
         <f>MAP!C13</f>
         <v>黒</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21" t="str">
+      <c r="F13" s="22"/>
+      <c r="G13" s="22" t="str">
         <f>MAP!D13</f>
         <v>黒</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21">
+      <c r="H13" s="22"/>
+      <c r="I13" s="22">
         <f>MAP!E13</f>
         <v>0</v>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="21" t="str">
+      <c r="B14" s="22" t="str">
         <f>MAP!A14</f>
         <v>外</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21" t="str">
+      <c r="C14" s="22"/>
+      <c r="D14" s="22" t="str">
         <f>MAP!B14</f>
         <v>黒</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21" t="str">
+      <c r="E14" s="22"/>
+      <c r="F14" s="22" t="str">
         <f>MAP!C14</f>
         <v>黒</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21">
+      <c r="G14" s="22"/>
+      <c r="H14" s="22">
         <f>MAP!D14</f>
         <v>0</v>
       </c>
-      <c r="I14" s="21"/>
+      <c r="I14" s="22"/>
       <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="21">
+      <c r="A15" s="22">
         <f>MAP!A15</f>
         <v>0</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21" t="str">
+      <c r="B15" s="22"/>
+      <c r="C15" s="22" t="str">
         <f>MAP!B15</f>
         <v>黒</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21" t="str">
+      <c r="D15" s="22"/>
+      <c r="E15" s="22" t="str">
         <f>MAP!C15</f>
         <v>黒</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21" t="str">
+      <c r="F15" s="22"/>
+      <c r="G15" s="22" t="str">
         <f>MAP!D15</f>
         <v>黒</v>
       </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21">
+      <c r="H15" s="22"/>
+      <c r="I15" s="22">
         <f>MAP!E15</f>
         <v>0</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="22"/>
     </row>
     <row r="16" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="21">
+      <c r="B16" s="22">
         <f>MAP!A16</f>
         <v>0</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21" t="str">
+      <c r="C16" s="22"/>
+      <c r="D16" s="22" t="str">
         <f>MAP!B16</f>
         <v>異</v>
       </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21" t="str">
+      <c r="E16" s="22"/>
+      <c r="F16" s="22" t="str">
         <f>MAP!C16</f>
         <v>異</v>
       </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21" t="str">
+      <c r="G16" s="22"/>
+      <c r="H16" s="22" t="str">
         <f>MAP!D16</f>
         <v>外</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="22"/>
       <c r="J16" s="6"/>
     </row>
     <row r="17" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="21">
+      <c r="A17" s="22">
         <f>MAP!A17</f>
         <v>0</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21" t="str">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22" t="str">
         <f>MAP!B17</f>
         <v>異</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21" t="str">
+      <c r="D17" s="22"/>
+      <c r="E17" s="22" t="str">
         <f>MAP!C17</f>
         <v>異</v>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21" t="str">
+      <c r="F17" s="22"/>
+      <c r="G17" s="22" t="str">
         <f>MAP!D17</f>
         <v>異</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21">
+      <c r="H17" s="22"/>
+      <c r="I17" s="22">
         <f>MAP!E17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="22"/>
     </row>
     <row r="18" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="21" t="str">
+      <c r="B18" s="22" t="str">
         <f>MAP!A18</f>
         <v>外</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21" t="str">
+      <c r="C18" s="22"/>
+      <c r="D18" s="22" t="str">
         <f>MAP!B18</f>
         <v>異</v>
       </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21" t="str">
+      <c r="E18" s="22"/>
+      <c r="F18" s="22" t="str">
         <f>MAP!C18</f>
         <v>異</v>
       </c>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21">
+      <c r="G18" s="22"/>
+      <c r="H18" s="22">
         <f>MAP!D18</f>
         <v>0</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="22"/>
       <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="21">
+      <c r="A19" s="22">
         <f>MAP!A19</f>
         <v>0</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21" t="str">
+      <c r="B19" s="22"/>
+      <c r="C19" s="22" t="str">
         <f>MAP!B19</f>
         <v>異</v>
       </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21" t="str">
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="str">
         <f>MAP!C19</f>
         <v>異</v>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21" t="str">
+      <c r="F19" s="22"/>
+      <c r="G19" s="22" t="str">
         <f>MAP!D19</f>
         <v>異</v>
       </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21">
+      <c r="H19" s="22"/>
+      <c r="I19" s="22">
         <f>MAP!E19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="21"/>
+      <c r="J19" s="22"/>
     </row>
     <row r="20" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="21">
+      <c r="B20" s="22">
         <f>MAP!A20</f>
         <v>0</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21" t="str">
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="str">
         <f>MAP!B20</f>
         <v>異</v>
       </c>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21" t="str">
+      <c r="E20" s="22"/>
+      <c r="F20" s="22" t="str">
         <f>MAP!C20</f>
         <v>異</v>
       </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21" t="str">
+      <c r="G20" s="22"/>
+      <c r="H20" s="22" t="str">
         <f>MAP!D20</f>
         <v>外</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="22"/>
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="21">
+      <c r="A21" s="22">
         <f>MAP!A21</f>
         <v>0</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21" t="str">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22" t="str">
         <f>MAP!B21</f>
         <v>異</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21" t="str">
+      <c r="D21" s="22"/>
+      <c r="E21" s="22" t="str">
         <f>MAP!C21</f>
         <v>異</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21" t="str">
+      <c r="F21" s="22"/>
+      <c r="G21" s="22" t="str">
         <f>MAP!D21</f>
         <v>異</v>
       </c>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21">
+      <c r="H21" s="22"/>
+      <c r="I21" s="22">
         <f>MAP!E21</f>
         <v>0</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="22"/>
     </row>
     <row r="22" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="21" t="str">
+      <c r="B22" s="22" t="str">
         <f>MAP!A22</f>
         <v>外</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21" t="str">
+      <c r="C22" s="22"/>
+      <c r="D22" s="22" t="str">
         <f>MAP!B22</f>
         <v>異</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21" t="str">
+      <c r="E22" s="22"/>
+      <c r="F22" s="22" t="str">
         <f>MAP!C22</f>
         <v>異</v>
       </c>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21">
+      <c r="G22" s="22"/>
+      <c r="H22" s="22">
         <f>MAP!D22</f>
         <v>0</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="22"/>
       <c r="J22" s="6"/>
     </row>
     <row r="23" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="21">
+      <c r="A23" s="22">
         <f>MAP!A23</f>
         <v>0</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21" t="str">
+      <c r="B23" s="22"/>
+      <c r="C23" s="22" t="str">
         <f>MAP!B23</f>
         <v>異</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21" t="str">
+      <c r="D23" s="22"/>
+      <c r="E23" s="22" t="str">
         <f>MAP!C23</f>
         <v>異</v>
       </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21" t="str">
+      <c r="F23" s="22"/>
+      <c r="G23" s="22" t="str">
         <f>MAP!D23</f>
         <v>異</v>
       </c>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21">
+      <c r="H23" s="22"/>
+      <c r="I23" s="22">
         <f>MAP!E23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="22"/>
     </row>
     <row r="24" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="21">
+      <c r="B24" s="22">
         <f>MAP!A24</f>
         <v>0</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21" t="str">
+      <c r="C24" s="22"/>
+      <c r="D24" s="22" t="str">
         <f>MAP!B24</f>
         <v>金</v>
       </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21" t="str">
+      <c r="E24" s="22"/>
+      <c r="F24" s="22" t="str">
         <f>MAP!C24</f>
         <v>金</v>
       </c>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21">
+      <c r="G24" s="22"/>
+      <c r="H24" s="22">
         <f>MAP!D24</f>
         <v>0</v>
       </c>
-      <c r="I24" s="21"/>
+      <c r="I24" s="22"/>
       <c r="J24" s="6"/>
     </row>
     <row r="25" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="21" t="str">
+      <c r="A25" s="22" t="str">
         <f>MAP!A25</f>
         <v>金</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21" t="str">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22" t="str">
         <f>MAP!B25</f>
         <v>金</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21" t="str">
+      <c r="D25" s="22"/>
+      <c r="E25" s="22" t="str">
         <f>MAP!C25</f>
         <v>金</v>
       </c>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21">
+      <c r="F25" s="22"/>
+      <c r="G25" s="22">
         <f>MAP!D25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21">
+      <c r="H25" s="22"/>
+      <c r="I25" s="22">
         <f>MAP!E25</f>
         <v>0</v>
       </c>
-      <c r="J25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="21" t="str">
+      <c r="B26" s="22" t="str">
         <f>MAP!A26</f>
         <v>金</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21" t="str">
+      <c r="C26" s="22"/>
+      <c r="D26" s="22" t="str">
         <f>MAP!B26</f>
         <v>金</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21">
+      <c r="E26" s="22"/>
+      <c r="F26" s="22">
         <f>MAP!C26</f>
         <v>0</v>
       </c>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21" t="str">
+      <c r="G26" s="22"/>
+      <c r="H26" s="22" t="str">
         <f>MAP!D26</f>
         <v>顔</v>
       </c>
-      <c r="I26" s="21"/>
+      <c r="I26" s="22"/>
       <c r="J26" s="6"/>
     </row>
     <row r="27" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="21" t="str">
+      <c r="A27" s="22" t="str">
         <f>MAP!A27</f>
         <v>炎</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21" t="str">
+      <c r="B27" s="22"/>
+      <c r="C27" s="22" t="str">
         <f>MAP!B27</f>
         <v>炎</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21">
+      <c r="D27" s="22"/>
+      <c r="E27" s="22">
         <f>MAP!C27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21" t="str">
+      <c r="F27" s="22"/>
+      <c r="G27" s="22" t="str">
         <f>MAP!D27</f>
         <v>顔</v>
       </c>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21" t="str">
+      <c r="H27" s="22"/>
+      <c r="I27" s="22" t="str">
         <f>MAP!E27</f>
         <v>顔</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="22"/>
     </row>
     <row r="28" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="21" t="str">
+      <c r="B28" s="22" t="str">
         <f>MAP!A28</f>
         <v>炎</v>
       </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21" t="str">
+      <c r="C28" s="22"/>
+      <c r="D28" s="22" t="str">
         <f>MAP!B28</f>
         <v>炎</v>
       </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21">
+      <c r="E28" s="22"/>
+      <c r="F28" s="22">
         <f>MAP!C28</f>
         <v>0</v>
       </c>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21" t="str">
+      <c r="G28" s="22"/>
+      <c r="H28" s="22" t="str">
         <f>MAP!D28</f>
         <v>顔</v>
       </c>
-      <c r="I28" s="21"/>
+      <c r="I28" s="22"/>
       <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="21" t="str">
+      <c r="A29" s="22" t="str">
         <f>MAP!A29</f>
         <v>炎</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21" t="str">
+      <c r="B29" s="22"/>
+      <c r="C29" s="22" t="str">
         <f>MAP!B29</f>
         <v>炎</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21">
+      <c r="D29" s="22"/>
+      <c r="E29" s="22">
         <f>MAP!C29</f>
         <v>0</v>
       </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21" t="str">
+      <c r="F29" s="22"/>
+      <c r="G29" s="22" t="str">
         <f>MAP!D29</f>
         <v>顔</v>
       </c>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21" t="str">
+      <c r="H29" s="22"/>
+      <c r="I29" s="22" t="str">
         <f>MAP!E29</f>
         <v>顔</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="22"/>
     </row>
     <row r="30" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="21" t="str">
+      <c r="B30" s="22" t="str">
         <f>MAP!A30</f>
         <v>炎</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21" t="str">
+      <c r="C30" s="22"/>
+      <c r="D30" s="22" t="str">
         <f>MAP!B30</f>
         <v>炎</v>
       </c>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21">
+      <c r="E30" s="22"/>
+      <c r="F30" s="22">
         <f>MAP!C30</f>
         <v>0</v>
       </c>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21" t="str">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22" t="str">
         <f>MAP!D30</f>
         <v>顔</v>
       </c>
-      <c r="I30" s="21"/>
+      <c r="I30" s="22"/>
       <c r="J30" s="6"/>
     </row>
     <row r="31" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="21" t="str">
+      <c r="A31" s="22" t="str">
         <f>MAP!A31</f>
         <v>炎</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21" t="str">
+      <c r="B31" s="22"/>
+      <c r="C31" s="22" t="str">
         <f>MAP!B31</f>
         <v>炎</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21">
+      <c r="D31" s="22"/>
+      <c r="E31" s="22">
         <f>MAP!C31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21" t="str">
+      <c r="F31" s="22"/>
+      <c r="G31" s="22" t="str">
         <f>MAP!D31</f>
         <v>顔</v>
       </c>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21" t="str">
+      <c r="H31" s="22"/>
+      <c r="I31" s="22" t="str">
         <f>MAP!E31</f>
         <v>顔</v>
       </c>
-      <c r="J31" s="21"/>
+      <c r="J31" s="22"/>
     </row>
     <row r="32" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="21" t="str">
+      <c r="B32" s="22" t="str">
         <f>MAP!A32</f>
         <v>炎</v>
       </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21" t="str">
+      <c r="C32" s="22"/>
+      <c r="D32" s="22" t="str">
         <f>MAP!B32</f>
         <v>炎</v>
       </c>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21">
+      <c r="E32" s="22"/>
+      <c r="F32" s="22">
         <f>MAP!C32</f>
         <v>0</v>
       </c>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21" t="str">
+      <c r="G32" s="22"/>
+      <c r="H32" s="22" t="str">
         <f>MAP!D32</f>
         <v>顔</v>
       </c>
-      <c r="I32" s="21"/>
+      <c r="I32" s="22"/>
       <c r="J32" s="6"/>
     </row>
     <row r="33" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="21" t="str">
+      <c r="A33" s="22" t="str">
         <f>MAP!A33</f>
         <v>炎</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21" t="str">
+      <c r="B33" s="22"/>
+      <c r="C33" s="22" t="str">
         <f>MAP!B33</f>
         <v>炎</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21">
+      <c r="D33" s="22"/>
+      <c r="E33" s="22">
         <f>MAP!C33</f>
         <v>0</v>
       </c>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21" t="str">
+      <c r="F33" s="22"/>
+      <c r="G33" s="22" t="str">
         <f>MAP!D33</f>
         <v>顔</v>
       </c>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21" t="str">
+      <c r="H33" s="22"/>
+      <c r="I33" s="22" t="str">
         <f>MAP!E33</f>
         <v>顔</v>
       </c>
-      <c r="J33" s="21"/>
+      <c r="J33" s="22"/>
     </row>
     <row r="34" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="21" t="str">
+      <c r="B34" s="22" t="str">
         <f>MAP!A34</f>
         <v>顔</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21" t="str">
+      <c r="C34" s="22"/>
+      <c r="D34" s="22" t="str">
         <f>MAP!B34</f>
         <v>顔</v>
       </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21" t="str">
+      <c r="E34" s="22"/>
+      <c r="F34" s="22" t="str">
         <f>MAP!C34</f>
         <v>顔</v>
       </c>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21" t="str">
+      <c r="G34" s="22"/>
+      <c r="H34" s="22" t="str">
         <f>MAP!D34</f>
         <v>顔</v>
       </c>
-      <c r="I34" s="21"/>
+      <c r="I34" s="22"/>
       <c r="J34" s="6"/>
     </row>
     <row r="35" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="21">
+      <c r="A35" s="22">
         <f>MAP!A35</f>
         <v>0</v>
       </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21" t="str">
+      <c r="B35" s="22"/>
+      <c r="C35" s="22" t="str">
         <f>MAP!B35</f>
         <v>顔</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21" t="str">
+      <c r="D35" s="22"/>
+      <c r="E35" s="22" t="str">
         <f>MAP!C35</f>
         <v>顔</v>
       </c>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21" t="str">
+      <c r="F35" s="22"/>
+      <c r="G35" s="22" t="str">
         <f>MAP!D35</f>
         <v>顔</v>
       </c>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21">
+      <c r="H35" s="22"/>
+      <c r="I35" s="22">
         <f>MAP!E35</f>
         <v>0</v>
       </c>
-      <c r="J35" s="21"/>
+      <c r="J35" s="22"/>
     </row>
     <row r="36" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <f>MAP!A36</f>
         <v>0</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21" t="str">
+      <c r="C36" s="22"/>
+      <c r="D36" s="22" t="str">
         <f>MAP!B36</f>
         <v>氷</v>
       </c>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21" t="str">
+      <c r="E36" s="22"/>
+      <c r="F36" s="22" t="str">
         <f>MAP!C36</f>
         <v>氷</v>
       </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21">
+      <c r="G36" s="22"/>
+      <c r="H36" s="22">
         <f>MAP!D36</f>
         <v>0</v>
       </c>
-      <c r="I36" s="21"/>
+      <c r="I36" s="22"/>
       <c r="J36" s="6"/>
     </row>
     <row r="37" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="21">
+      <c r="A37" s="22">
         <f>MAP!A37</f>
         <v>0</v>
       </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21" t="str">
+      <c r="B37" s="22"/>
+      <c r="C37" s="22" t="str">
         <f>MAP!B37</f>
         <v>氷</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21" t="str">
+      <c r="D37" s="22"/>
+      <c r="E37" s="22" t="str">
         <f>MAP!C37</f>
         <v>氷</v>
       </c>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21" t="str">
+      <c r="F37" s="22"/>
+      <c r="G37" s="22" t="str">
         <f>MAP!D37</f>
         <v>氷</v>
       </c>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21">
+      <c r="H37" s="22"/>
+      <c r="I37" s="22">
         <f>MAP!E37</f>
         <v>0</v>
       </c>
-      <c r="J37" s="21"/>
+      <c r="J37" s="22"/>
     </row>
     <row r="38" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="21">
+      <c r="B38" s="22">
         <f>MAP!A38</f>
         <v>0</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21" t="str">
+      <c r="C38" s="22"/>
+      <c r="D38" s="22" t="str">
         <f>MAP!B38</f>
         <v>氷</v>
       </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21" t="str">
+      <c r="E38" s="22"/>
+      <c r="F38" s="22" t="str">
         <f>MAP!C38</f>
         <v>氷</v>
       </c>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21">
+      <c r="G38" s="22"/>
+      <c r="H38" s="22">
         <f>MAP!D38</f>
         <v>0</v>
       </c>
-      <c r="I38" s="21"/>
+      <c r="I38" s="22"/>
       <c r="J38" s="6"/>
     </row>
     <row r="39" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="21">
+      <c r="A39" s="22">
         <f>MAP!A39</f>
         <v>0</v>
       </c>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21" t="str">
+      <c r="B39" s="22"/>
+      <c r="C39" s="22" t="str">
         <f>MAP!B39</f>
         <v>氷</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21" t="str">
+      <c r="D39" s="22"/>
+      <c r="E39" s="22" t="str">
         <f>MAP!C39</f>
         <v>氷</v>
       </c>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21" t="str">
+      <c r="F39" s="22"/>
+      <c r="G39" s="22" t="str">
         <f>MAP!D39</f>
         <v>氷</v>
       </c>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21">
+      <c r="H39" s="22"/>
+      <c r="I39" s="22">
         <f>MAP!E39</f>
         <v>0</v>
       </c>
-      <c r="J39" s="21"/>
+      <c r="J39" s="22"/>
     </row>
     <row r="40" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="21">
+      <c r="B40" s="22">
         <f>MAP!A40</f>
         <v>0</v>
       </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21" t="str">
+      <c r="C40" s="22"/>
+      <c r="D40" s="22" t="str">
         <f>MAP!B40</f>
         <v>氷</v>
       </c>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21" t="str">
+      <c r="E40" s="22"/>
+      <c r="F40" s="22" t="str">
         <f>MAP!C40</f>
         <v>氷</v>
       </c>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21">
+      <c r="G40" s="22"/>
+      <c r="H40" s="22">
         <f>MAP!D40</f>
         <v>0</v>
       </c>
-      <c r="I40" s="21"/>
+      <c r="I40" s="22"/>
       <c r="J40" s="6"/>
     </row>
     <row r="41" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="21">
+      <c r="A41" s="22">
         <f>MAP!A41</f>
         <v>0</v>
       </c>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21" t="str">
+      <c r="B41" s="22"/>
+      <c r="C41" s="22" t="str">
         <f>MAP!B41</f>
         <v>氷</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21" t="str">
+      <c r="D41" s="22"/>
+      <c r="E41" s="22" t="str">
         <f>MAP!C41</f>
         <v>氷</v>
       </c>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21" t="str">
+      <c r="F41" s="22"/>
+      <c r="G41" s="22" t="str">
         <f>MAP!D41</f>
         <v>氷</v>
       </c>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21">
+      <c r="H41" s="22"/>
+      <c r="I41" s="22">
         <f>MAP!E41</f>
         <v>0</v>
       </c>
-      <c r="J41" s="21"/>
+      <c r="J41" s="22"/>
     </row>
     <row r="42" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="21" t="str">
+      <c r="B42" s="22" t="str">
         <f>MAP!A42</f>
         <v>樹</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21" t="str">
+      <c r="C42" s="22"/>
+      <c r="D42" s="22" t="str">
         <f>MAP!B42</f>
         <v>樹</v>
       </c>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21" t="str">
+      <c r="E42" s="22"/>
+      <c r="F42" s="22" t="str">
         <f>MAP!C42</f>
         <v>樹</v>
       </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21" t="str">
+      <c r="G42" s="22"/>
+      <c r="H42" s="22" t="str">
         <f>MAP!D42</f>
         <v>樹</v>
       </c>
-      <c r="I42" s="21"/>
+      <c r="I42" s="22"/>
       <c r="J42" s="6"/>
     </row>
     <row r="43" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="21" t="str">
+      <c r="A43" s="22" t="str">
         <f>MAP!A43</f>
         <v>骨</v>
       </c>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21">
+      <c r="B43" s="22"/>
+      <c r="C43" s="22">
         <f>MAP!B43</f>
         <v>0</v>
       </c>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21" t="str">
+      <c r="D43" s="22"/>
+      <c r="E43" s="22" t="str">
         <f>MAP!C43</f>
         <v>樹</v>
       </c>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21" t="str">
+      <c r="F43" s="22"/>
+      <c r="G43" s="22" t="str">
         <f>MAP!D43</f>
         <v>樹</v>
       </c>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21" t="str">
+      <c r="H43" s="22"/>
+      <c r="I43" s="22" t="str">
         <f>MAP!E43</f>
         <v>樹</v>
       </c>
-      <c r="J43" s="21"/>
+      <c r="J43" s="22"/>
     </row>
     <row r="44" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="21" t="str">
+      <c r="B44" s="22" t="str">
         <f>MAP!A44</f>
         <v>骨</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21">
+      <c r="C44" s="22"/>
+      <c r="D44" s="22">
         <f>MAP!B44</f>
         <v>0</v>
       </c>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21" t="str">
+      <c r="E44" s="22"/>
+      <c r="F44" s="22" t="str">
         <f>MAP!C44</f>
         <v>樹</v>
       </c>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21" t="str">
+      <c r="G44" s="22"/>
+      <c r="H44" s="22" t="str">
         <f>MAP!D44</f>
         <v>樹</v>
       </c>
-      <c r="I44" s="21"/>
+      <c r="I44" s="22"/>
       <c r="J44" s="6"/>
     </row>
     <row r="45" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="21" t="str">
+      <c r="A45" s="22" t="str">
         <f>MAP!A45</f>
         <v>骨</v>
       </c>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21">
+      <c r="B45" s="22"/>
+      <c r="C45" s="22">
         <f>MAP!B45</f>
         <v>0</v>
       </c>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21" t="str">
+      <c r="D45" s="22"/>
+      <c r="E45" s="22" t="str">
         <f>MAP!C45</f>
         <v>樹</v>
       </c>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21" t="str">
+      <c r="F45" s="22"/>
+      <c r="G45" s="22" t="str">
         <f>MAP!D45</f>
         <v>樹</v>
       </c>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21" t="str">
+      <c r="H45" s="22"/>
+      <c r="I45" s="22" t="str">
         <f>MAP!E45</f>
         <v>樹</v>
       </c>
-      <c r="J45" s="21"/>
+      <c r="J45" s="22"/>
     </row>
     <row r="46" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="21" t="str">
+      <c r="B46" s="22" t="str">
         <f>MAP!A46</f>
         <v>骨</v>
       </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21">
+      <c r="C46" s="22"/>
+      <c r="D46" s="22">
         <f>MAP!B46</f>
         <v>0</v>
       </c>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21" t="str">
+      <c r="E46" s="22"/>
+      <c r="F46" s="22" t="str">
         <f>MAP!C46</f>
         <v>樹</v>
       </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21" t="str">
+      <c r="G46" s="22"/>
+      <c r="H46" s="22" t="str">
         <f>MAP!D46</f>
         <v>樹</v>
       </c>
-      <c r="I46" s="21"/>
+      <c r="I46" s="22"/>
       <c r="J46" s="6"/>
     </row>
     <row r="47" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="21" t="str">
+      <c r="A47" s="22" t="str">
         <f>MAP!A47</f>
         <v>骨</v>
       </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21">
+      <c r="B47" s="22"/>
+      <c r="C47" s="22">
         <f>MAP!B47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21" t="str">
+      <c r="D47" s="22"/>
+      <c r="E47" s="22" t="str">
         <f>MAP!C47</f>
         <v>樹</v>
       </c>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21" t="str">
+      <c r="F47" s="22"/>
+      <c r="G47" s="22" t="str">
         <f>MAP!D47</f>
         <v>樹</v>
       </c>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21" t="str">
+      <c r="H47" s="22"/>
+      <c r="I47" s="22" t="str">
         <f>MAP!E47</f>
         <v>樹</v>
       </c>
-      <c r="J47" s="21"/>
+      <c r="J47" s="22"/>
     </row>
     <row r="48" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="21" t="str">
+      <c r="B48" s="22" t="str">
         <f>MAP!A48</f>
         <v>骨</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21">
+      <c r="C48" s="22"/>
+      <c r="D48" s="22">
         <f>MAP!B48</f>
         <v>0</v>
       </c>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21" t="str">
+      <c r="E48" s="22"/>
+      <c r="F48" s="22" t="str">
         <f>MAP!C48</f>
         <v>樹</v>
       </c>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21" t="str">
+      <c r="G48" s="22"/>
+      <c r="H48" s="22" t="str">
         <f>MAP!D48</f>
         <v>樹</v>
       </c>
-      <c r="I48" s="21"/>
+      <c r="I48" s="22"/>
       <c r="J48" s="6"/>
     </row>
     <row r="49" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="21" t="str">
+      <c r="A49" s="22" t="str">
         <f>MAP!A49</f>
         <v>骨</v>
       </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21">
+      <c r="B49" s="22"/>
+      <c r="C49" s="22">
         <f>MAP!B49</f>
         <v>0</v>
       </c>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21" t="str">
+      <c r="D49" s="22"/>
+      <c r="E49" s="22" t="str">
         <f>MAP!C49</f>
         <v>樹</v>
       </c>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21" t="str">
+      <c r="F49" s="22"/>
+      <c r="G49" s="22" t="str">
         <f>MAP!D49</f>
         <v>樹</v>
       </c>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21">
+      <c r="H49" s="22"/>
+      <c r="I49" s="22">
         <f>MAP!E49</f>
         <v>0</v>
       </c>
-      <c r="J49" s="21"/>
+      <c r="J49" s="22"/>
     </row>
     <row r="50" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="21">
+      <c r="B50" s="22">
         <f>MAP!A50</f>
         <v>0</v>
       </c>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21" t="str">
+      <c r="C50" s="22"/>
+      <c r="D50" s="22" t="str">
         <f>MAP!B50</f>
         <v>石</v>
       </c>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21" t="str">
+      <c r="E50" s="22"/>
+      <c r="F50" s="22" t="str">
         <f>MAP!C50</f>
         <v>石</v>
       </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21">
+      <c r="G50" s="22"/>
+      <c r="H50" s="22">
         <f>MAP!D50</f>
         <v>0</v>
       </c>
-      <c r="I50" s="21"/>
+      <c r="I50" s="22"/>
       <c r="J50" s="6"/>
     </row>
     <row r="51" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="21">
+      <c r="A51" s="22">
         <f>MAP!A51</f>
         <v>0</v>
       </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21" t="str">
+      <c r="B51" s="22"/>
+      <c r="C51" s="22" t="str">
         <f>MAP!B51</f>
         <v>石</v>
       </c>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21" t="str">
+      <c r="D51" s="22"/>
+      <c r="E51" s="22" t="str">
         <f>MAP!C51</f>
         <v>石</v>
       </c>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21" t="str">
+      <c r="F51" s="22"/>
+      <c r="G51" s="22" t="str">
         <f>MAP!D51</f>
         <v>石</v>
       </c>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21">
+      <c r="H51" s="22"/>
+      <c r="I51" s="22">
         <f>MAP!E51</f>
         <v>0</v>
       </c>
-      <c r="J51" s="21"/>
+      <c r="J51" s="22"/>
     </row>
     <row r="52" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="21">
+      <c r="B52" s="22">
         <f>MAP!A52</f>
         <v>0</v>
       </c>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21" t="str">
+      <c r="C52" s="22"/>
+      <c r="D52" s="22" t="str">
         <f>MAP!B52</f>
         <v>石</v>
       </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21" t="str">
+      <c r="E52" s="22"/>
+      <c r="F52" s="22" t="str">
         <f>MAP!C52</f>
         <v>石</v>
       </c>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21">
+      <c r="G52" s="22"/>
+      <c r="H52" s="22">
         <f>MAP!D52</f>
         <v>0</v>
       </c>
-      <c r="I52" s="21"/>
+      <c r="I52" s="22"/>
       <c r="J52" s="6"/>
     </row>
     <row r="53" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="21">
+      <c r="A53" s="22">
         <f>MAP!A53</f>
         <v>0</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21" t="str">
+      <c r="B53" s="22"/>
+      <c r="C53" s="22" t="str">
         <f>MAP!B53</f>
         <v>石</v>
       </c>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21" t="str">
+      <c r="D53" s="22"/>
+      <c r="E53" s="22" t="str">
         <f>MAP!C53</f>
         <v>石</v>
       </c>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21" t="str">
+      <c r="F53" s="22"/>
+      <c r="G53" s="22" t="str">
         <f>MAP!D53</f>
         <v>石</v>
       </c>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21">
+      <c r="H53" s="22"/>
+      <c r="I53" s="22">
         <f>MAP!E53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="21"/>
+      <c r="J53" s="22"/>
     </row>
     <row r="54" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="21">
+      <c r="B54" s="22">
         <f>MAP!A54</f>
         <v>0</v>
       </c>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21" t="str">
+      <c r="C54" s="22"/>
+      <c r="D54" s="22" t="str">
         <f>MAP!B54</f>
         <v>石</v>
       </c>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21" t="str">
+      <c r="E54" s="22"/>
+      <c r="F54" s="22" t="str">
         <f>MAP!C54</f>
         <v>石</v>
       </c>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21">
+      <c r="G54" s="22"/>
+      <c r="H54" s="22">
         <f>MAP!D54</f>
         <v>0</v>
       </c>
-      <c r="I54" s="21"/>
+      <c r="I54" s="22"/>
       <c r="J54" s="6"/>
     </row>
     <row r="55" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="21">
+      <c r="A55" s="22">
         <f>MAP!A55</f>
         <v>0</v>
       </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21" t="str">
+      <c r="B55" s="22"/>
+      <c r="C55" s="22" t="str">
         <f>MAP!B55</f>
         <v>石</v>
       </c>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21" t="str">
+      <c r="D55" s="22"/>
+      <c r="E55" s="22" t="str">
         <f>MAP!C55</f>
         <v>石</v>
       </c>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21" t="str">
+      <c r="F55" s="22"/>
+      <c r="G55" s="22" t="str">
         <f>MAP!D55</f>
         <v>石</v>
       </c>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21">
+      <c r="H55" s="22"/>
+      <c r="I55" s="22">
         <f>MAP!E55</f>
         <v>0</v>
       </c>
-      <c r="J55" s="21"/>
+      <c r="J55" s="22"/>
     </row>
     <row r="56" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="21">
+      <c r="B56" s="22">
         <f>MAP!A56</f>
         <v>0</v>
       </c>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21" t="str">
+      <c r="C56" s="22"/>
+      <c r="D56" s="22" t="str">
         <f>MAP!B56</f>
         <v>街</v>
       </c>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21" t="str">
+      <c r="E56" s="22"/>
+      <c r="F56" s="22" t="str">
         <f>MAP!C56</f>
         <v>街</v>
       </c>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21">
+      <c r="G56" s="22"/>
+      <c r="H56" s="22">
         <f>MAP!D56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="21"/>
+      <c r="I56" s="22"/>
       <c r="J56" s="6"/>
     </row>
     <row r="57" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="21">
+      <c r="A57" s="22">
         <f>MAP!A57</f>
         <v>0</v>
       </c>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21" t="str">
+      <c r="B57" s="22"/>
+      <c r="C57" s="22" t="str">
         <f>MAP!B57</f>
         <v>街</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21" t="str">
+      <c r="D57" s="22"/>
+      <c r="E57" s="22" t="str">
         <f>MAP!C57</f>
         <v>街</v>
       </c>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21" t="str">
+      <c r="F57" s="22"/>
+      <c r="G57" s="22" t="str">
         <f>MAP!D57</f>
         <v>街</v>
       </c>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21">
+      <c r="H57" s="22"/>
+      <c r="I57" s="22">
         <f>MAP!E57</f>
         <v>0</v>
       </c>
-      <c r="J57" s="21"/>
+      <c r="J57" s="22"/>
     </row>
     <row r="58" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="21">
+      <c r="B58" s="22">
         <f>MAP!A58</f>
         <v>0</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21" t="str">
+      <c r="C58" s="22"/>
+      <c r="D58" s="22" t="str">
         <f>MAP!B58</f>
         <v>街</v>
       </c>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21" t="str">
+      <c r="E58" s="22"/>
+      <c r="F58" s="22" t="str">
         <f>MAP!C58</f>
         <v>街</v>
       </c>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21">
+      <c r="G58" s="22"/>
+      <c r="H58" s="22">
         <f>MAP!D58</f>
         <v>0</v>
       </c>
-      <c r="I58" s="21"/>
+      <c r="I58" s="22"/>
       <c r="J58" s="6"/>
     </row>
     <row r="59" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="21">
+      <c r="A59" s="22">
         <f>MAP!A59</f>
         <v>0</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21" t="str">
+      <c r="B59" s="22"/>
+      <c r="C59" s="22" t="str">
         <f>MAP!B59</f>
         <v>街</v>
       </c>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21" t="str">
+      <c r="D59" s="22"/>
+      <c r="E59" s="22" t="str">
         <f>MAP!C59</f>
         <v>街</v>
       </c>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21" t="str">
+      <c r="F59" s="22"/>
+      <c r="G59" s="22" t="str">
         <f>MAP!D59</f>
         <v>街</v>
       </c>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21">
+      <c r="H59" s="22"/>
+      <c r="I59" s="22">
         <f>MAP!E59</f>
         <v>0</v>
       </c>
-      <c r="J59" s="21"/>
+      <c r="J59" s="22"/>
     </row>
     <row r="60" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B60" s="21">
+      <c r="B60" s="22">
         <f>MAP!A60</f>
         <v>0</v>
       </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21" t="str">
+      <c r="C60" s="22"/>
+      <c r="D60" s="22" t="str">
         <f>MAP!B60</f>
         <v>街</v>
       </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21" t="str">
+      <c r="E60" s="22"/>
+      <c r="F60" s="22" t="str">
         <f>MAP!C60</f>
         <v>街</v>
       </c>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21">
+      <c r="G60" s="22"/>
+      <c r="H60" s="22">
         <f>MAP!D60</f>
         <v>0</v>
       </c>
-      <c r="I60" s="21"/>
+      <c r="I60" s="22"/>
       <c r="J60" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="270">
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
@@ -7088,258 +8452,6 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:I60"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7352,8 +8464,8 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B2" s="22" t="s">
-        <v>165</v>
+      <c r="B2" s="21" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.4">
@@ -7361,7 +8473,7 @@
         <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.4">
@@ -7369,15 +8481,15 @@
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.4">
@@ -7385,7 +8497,7 @@
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.4">
@@ -7393,7 +8505,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.4">
@@ -7401,7 +8513,7 @@
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.4">
@@ -7409,15 +8521,15 @@
         <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.4">
@@ -7425,15 +8537,15 @@
         <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.4">
@@ -7441,7 +8553,7 @@
         <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.4">
@@ -7449,7 +8561,7 @@
         <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.4">
@@ -7457,7 +8569,7 @@
         <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
@@ -7465,7 +8577,7 @@
         <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
@@ -7473,7 +8585,7 @@
         <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
@@ -7481,15 +8593,15 @@
         <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
